--- a/_concept_6G_integration/MCS_Fall_Detection.xlsx
+++ b/_concept_6G_integration/MCS_Fall_Detection.xlsx
@@ -5,16 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mcsdatalabsgmbh-my.sharepoint.com/personal/hayate_sato_mcs-datalabs_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hayat\Documents\6G\FallDetection_new\_concept_6G_integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{C61EB59A-694A-4213-9C1F-4B1C589E2315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC00980E-6203-4927-9A21-2ECC2220B4B0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD13B08E-4F33-4A1E-82A3-CBC245718F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="-2970" windowWidth="23232" windowHeight="13872" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
+    <workbookView xWindow="7470" yWindow="3675" windowWidth="25995" windowHeight="13875" activeTab="3" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Architecture" sheetId="3" r:id="rId3"/>
+    <sheet name="SequenceDiagram" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="65">
   <si>
     <t>1.</t>
   </si>
@@ -236,12 +238,66 @@
   <si>
     <t>Andreea?</t>
   </si>
+  <si>
+    <t xml:space="preserve">Additional Components </t>
+  </si>
+  <si>
+    <t>Exsisting Components</t>
+  </si>
+  <si>
+    <t>POST / Predict</t>
+  </si>
+  <si>
+    <t>(sending raw data)</t>
+  </si>
+  <si>
+    <t>Send ACC data</t>
+  </si>
+  <si>
+    <t>(every XX sec)</t>
+  </si>
+  <si>
+    <t>Publish Fall</t>
+  </si>
+  <si>
+    <t>Send confirmation message</t>
+  </si>
+  <si>
+    <t>(Patient ID, confidence level)</t>
+  </si>
+  <si>
+    <t>Did you fall? (T/F)</t>
+  </si>
+  <si>
+    <t>Do you need help? (T/F)</t>
+  </si>
+  <si>
+    <t>Fallback: send help</t>
+  </si>
+  <si>
+    <t>Alert message</t>
+  </si>
+  <si>
+    <t>Patient XX fell, needs help</t>
+  </si>
+  <si>
+    <t>Help requested @ HH:MM:SSS</t>
+  </si>
+  <si>
+    <t>Fall confirmed @ HH:MM:SSS</t>
+  </si>
+  <si>
+    <t>No Reponse @ HH:MM:SSS</t>
+  </si>
+  <si>
+    <t>Response</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,8 +336,22 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -294,8 +364,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -312,11 +394,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -324,6 +415,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2390,6 +2491,6313 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>16362</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>67234</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>593911</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>179293</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Rectangle 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18E6BDB1-FB66-41C7-AEE4-A7EA73478DCB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2436833" y="257734"/>
+          <a:ext cx="9049196" cy="2801471"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="dash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>186690</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>62865</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EED4C0B-B79A-49C2-9524-052611A1F244}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1396925" y="3704777"/>
+          <a:ext cx="10109835" cy="5002194"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="dash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>416635</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>121136</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>214705</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>155426</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF5D8E8A-35BA-464B-86D7-8663888A6FC0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="416635" y="1264136"/>
+          <a:ext cx="1017270" cy="624840"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SamrKo</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>43253</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>471207</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10420</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35B312A7-5BA2-43C9-B0FA-C548BC32D814}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2463724" y="100853"/>
+          <a:ext cx="1033071" cy="290567"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Mobile App</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>125730</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>118110</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rectangle 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{023D984C-2B84-43A7-AFC1-1A409F328018}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2564130" y="2895600"/>
+          <a:ext cx="1036320" cy="651510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>InfluxDB</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>72391</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>190501</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>109904</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangle 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D70B74BF-EB61-409C-AF90-3089426F7ABC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4937468" y="4144694"/>
+          <a:ext cx="5591321" cy="3218864"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="dash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Rectangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84703822-5F99-470D-AEB5-B0949F0422C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2571750" y="3794760"/>
+          <a:ext cx="1032510" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FHIR</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> DB</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>606799</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>185010</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>420108</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>70710</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Rectangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D97889AF-DA54-4A0E-AB55-FF0B0E7A031A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5483599" y="5728560"/>
+          <a:ext cx="1032509" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Data Preprocessor</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>499110</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>188595</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>308610</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>74295</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Rectangle 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{616B7331-EA63-41E0-8CA9-9E41D019BF60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9033510" y="3046095"/>
+          <a:ext cx="1028700" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MQTT</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> Publisher</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>361726</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>143996</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>175708</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>29696</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Rectangle 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5934A74B-F273-4B51-B745-51F45D7CF51B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7067326" y="5497046"/>
+          <a:ext cx="1033182" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Model</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Updater</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>110490</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>146538</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Rectangle 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C70BC7D-D097-4E84-9430-A21552E3AAD3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2062529" y="4125644"/>
+          <a:ext cx="1997759" cy="3274548"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="dash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>510247</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>31360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>127342</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>82794</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Rectangle 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82F938B8-CDAC-4BA3-90D0-ABB3CD654390}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2334651" y="4237014"/>
+          <a:ext cx="1441499" cy="241934"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Current System</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>420332</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>493058</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Rectangle 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82CBD3B6-844D-441D-A064-7978E54D12D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14943156" y="1154206"/>
+          <a:ext cx="677843" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>23420</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>122817</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>438038</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>8517</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Rectangle 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DCF0CBA-C90E-41F9-8F59-75EE244399C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7284832" y="1265817"/>
+          <a:ext cx="1019735" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Fall confirmation</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>187362</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>57933</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>5154</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>50313</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Rectangle 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78C88867-A0EA-40B5-A536-113778EDD4D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18340891" y="3128345"/>
+          <a:ext cx="1028028" cy="563880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>API Caller</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>82252</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>59279</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>67684</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>160244</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="Rectangle 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{197C1DC9-CBB2-4DCA-87A3-FE2BA6296580}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20051134" y="3320191"/>
+          <a:ext cx="1195668" cy="672465"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Data fetcher</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="800" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(for  inference)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>601644</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>118335</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>411144</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>4035</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="Rectangle 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{098F9CA5-B4C2-4909-82F8-C67F4DBE2B2A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9073291" y="1261335"/>
+          <a:ext cx="1019735" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MQTT subscriber</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>296285</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>30370</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>105784</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>128982</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Rectangle 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3311CC3-5A8E-410E-8FEB-FBF9D196E5E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5782685" y="2144920"/>
+          <a:ext cx="1028699" cy="670112"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Influx Writer</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>240477</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>96371</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>63312</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>5938</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="Rectangle 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10545403-86D7-453F-8402-DB1A02A20D9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1450712" y="3525371"/>
+          <a:ext cx="1033071" cy="290567"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Backend</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>409016</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>459442</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="Rectangle 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69B086C4-4A40-4D94-802E-D5D40553D5D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14931840" y="1524000"/>
+          <a:ext cx="655543" cy="220532"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>551553</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>145229</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>369905</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>30929</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Rectangle 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB419F36-7831-4631-AD43-8C71165FF4DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7866753" y="6260279"/>
+          <a:ext cx="1037552" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Postgres</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(inference</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> log)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>574750</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>13000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>384250</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>111612</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="Rectangle 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38ACA35A-CBE3-4B0B-9B11-6AD0658D39EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7231044" y="2130912"/>
+          <a:ext cx="1019735" cy="670112"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>API caller</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>235323</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>165932</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>65079</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="Rectangle 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6B4440C-2A51-422C-8A8A-3879206BA0ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1451592" y="9134086"/>
+          <a:ext cx="10066331" cy="1613647"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>420221</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>177140</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>219808</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>117524</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectangle 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA2E3CA5-1436-4C6B-94F2-48CF8C7A06C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1636490" y="8954794"/>
+          <a:ext cx="1623991" cy="321384"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Web App / Front</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> end</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>413117</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>82949</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>235953</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>159149</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Rectangle 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2760CBFA-34C6-4E90-9A96-9E5E0CD3F164}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8927002" y="9813103"/>
+          <a:ext cx="1039105" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Dashboard</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(Syste</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>m Health</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>255631</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>108205</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>234461</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>184405</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Rectangle 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{535B0D64-E04C-49EC-984C-F91E9A6D5DB7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4512573" y="9838359"/>
+          <a:ext cx="1195100" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Dashboard</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(patient monitoring)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1000">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>246529</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>14654</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>372036</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>155287</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="Rectangle 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D880C06-FEA6-4281-AEA6-2D366DE29D04}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7544144" y="9363808"/>
+          <a:ext cx="3774315" cy="1283633"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="dash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>556845</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>14654</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>513231</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>150805</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="Rectangle 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D507D40-A57E-4DC7-9BFC-3139D92699AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4205653" y="9363808"/>
+          <a:ext cx="2997059" cy="1279151"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="dash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>73269</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>42995</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>94429</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Rectangle 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB87A18F-B73D-423F-9977-8238C491F58B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6778869" y="4253045"/>
+          <a:ext cx="2241306" cy="241934"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Components MCS will build</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:srgbClr val="002060"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>168380</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>166089</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>322384</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>27023</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="Rectangle 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35B1F666-37A1-4BA3-B436-775BA564F5F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5033457" y="9515243"/>
+          <a:ext cx="1370273" cy="241934"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" b="1" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Caregiver User</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>343193</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>153847</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>565406</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>14781</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="Rectangle 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45992A6F-0A3B-4A86-8F7C-E994D7946016}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8857078" y="9503001"/>
+          <a:ext cx="1438482" cy="241934"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" b="1" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Admin User</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>336684</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>136367</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>150666</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>22067</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="Rectangle 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E1B47A4-7148-4901-9AE2-F78D1B353623}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18624684" y="5489417"/>
+          <a:ext cx="1033182" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Model</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Engine</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>128660</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>133789</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>732</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Rectangle 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DF8F53B-0B98-427A-BA5B-0B5E2CD748A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2567060" y="6439339"/>
+          <a:ext cx="1023865" cy="628943"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Data fetcher</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="800" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(for current dashboard)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>353037</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>96138</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>175873</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>172338</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="Rectangle 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3FB578D-F768-421D-ADD4-ED5534EC5F12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10083191" y="9826292"/>
+          <a:ext cx="1039105" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Dashboard</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(ml monitoring)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>484922</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>96137</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>307757</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>172337</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="Rectangle 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F88E607F-E889-457E-808E-CA36BB888F3B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7782537" y="9826291"/>
+          <a:ext cx="1039105" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>/Doc</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>378722</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>114067</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>357553</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>190267</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="Rectangle 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE7B0788-C10A-4322-A9ED-ACD9D3172987}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5851934" y="9844221"/>
+          <a:ext cx="1195100" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Dashboard</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(fall</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> history</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1000">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>211455</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>89535</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="Rectangle 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E96C4BA-5954-4CAA-B24C-9FAA1F8FCFD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3259455" y="1362075"/>
+          <a:ext cx="1036320" cy="651510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Data Collector</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>35299</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>108810</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>458208</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>185010</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="Rectangle 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FAD7A48-165B-40A3-A589-E5A337D4C822}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5521699" y="4699860"/>
+          <a:ext cx="1032509" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Inference</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>API</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>108150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BE0D88B-EAA8-4048-953B-FD1FD4726FFE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1304925" y="1200150"/>
+          <a:ext cx="1036320" cy="432000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Data Collector</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>108150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C87F8E83-CD8F-4FE5-8384-322A5AC03904}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3133725" y="1200150"/>
+          <a:ext cx="1036320" cy="432000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>API caller</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>108150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rectangle 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61E6D482-F54C-4B58-ADB0-4D03E373E3B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4962525" y="1200150"/>
+          <a:ext cx="1036320" cy="432000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Inference API</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1000">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>108150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangle 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C133F031-8859-4144-9B76-252B7D0E2B4D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6791325" y="1200150"/>
+          <a:ext cx="1036320" cy="432000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MQTT</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> Pub</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="900">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>108150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectangle 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1CEF3A0-E4DB-4903-A6EE-01C6F20F477E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8620125" y="1200150"/>
+          <a:ext cx="1036320" cy="432000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MQTT Sub</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>108150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Rectangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE878F51-E042-4C9B-9570-8432773A7982}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10448925" y="1200150"/>
+          <a:ext cx="1036320" cy="432000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Patient Response</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1000">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>108149</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Rectangle 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54619026-1CF5-485F-92A1-94EB05B16DE3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12277725" y="1200149"/>
+          <a:ext cx="1036320" cy="432000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Caregiver</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> Dashboard</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1000">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>142874</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Rectangle 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81BC54A5-0ABF-40DD-957C-02A5D34FA63F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="752474" y="304800"/>
+          <a:ext cx="4867276" cy="327660"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Fall Detection &amp; Notification Flow</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="2000" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="Straight Arrow Connector 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB64E026-3CBF-942C-4B96-EDE0797F3AE3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1895475" y="2247900"/>
+          <a:ext cx="1743075" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="Straight Arrow Connector 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C528404B-16AB-9E34-9707-44B5B2B2521E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3686175" y="2905125"/>
+          <a:ext cx="1743075" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="Straight Arrow Connector 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D9B5094-ED5C-3D8E-9290-6B199075E99F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5543550" y="4505325"/>
+          <a:ext cx="1743075" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>388620</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Rectangle 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F68E8B5-E84C-4BB0-99CD-590DCE02FF76}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4476750" y="3038475"/>
+          <a:ext cx="2007870" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Data preprocessor</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Resample &gt;</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> lsb/G &gt; last 9sec &gt; features </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="900">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="85000"/>
+                <a:lumOff val="15000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>369570</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Rectangle 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F18F5420-1353-DFC7-B088-511392563AD1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4457700" y="3495675"/>
+          <a:ext cx="2007870" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Result</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>confidence</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> &gt; 0.5 = Fall</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="900" b="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="85000"/>
+                <a:lumOff val="15000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="21" name="Straight Arrow Connector 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D209938-D997-453E-B007-71DF4425A66B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7381875" y="5143500"/>
+          <a:ext cx="1743075" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="26" name="Straight Arrow Connector 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34A7BC5E-52A3-4132-4EEB-B773173FD289}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9201150" y="5838825"/>
+          <a:ext cx="1743075" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="Straight Arrow Connector 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B693CC62-AEC5-DA4B-E488-078A9CDD89A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11039475" y="6343650"/>
+          <a:ext cx="1743075" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>180974</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Rectangle 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98DE5C4E-40CB-47F8-93E2-1BB2F31F581C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1314449" y="752475"/>
+          <a:ext cx="3133725" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Mobile</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> App</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="900" b="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>276224</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>323849</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Rectangle 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76F91650-6115-452C-EFB0-1FD3CBC4C3AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4543424" y="752475"/>
+          <a:ext cx="3705225" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Backend</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>447674</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="Rectangle 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D118053-1B06-4F8D-3B56-B8B60CB485FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8372474" y="752475"/>
+          <a:ext cx="3448051" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Mobile</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> App</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="900" b="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>200026</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Rectangle 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7545C4FA-1E5A-2AAC-8A18-670E16E30A51}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11944350" y="752475"/>
+          <a:ext cx="1666876" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Web</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> App</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="900" b="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>108150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Rectangle 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8DB16B1-36CD-40FF-96AE-0277A1B09345}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3147332" y="1200150"/>
+          <a:ext cx="1039042" cy="432000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>API caller</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>108150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="Rectangle 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2AEED4A-C8DC-44F1-94C2-B7EFCA8B0A15}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4984296" y="1200150"/>
+          <a:ext cx="1039042" cy="432000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Inference API</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1000">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>108150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Rectangle 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{414C838C-2089-4070-866C-319A035E2392}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6821261" y="1200150"/>
+          <a:ext cx="1039041" cy="432000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MQTT</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> Pub</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="900">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>108150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="Rectangle 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C5A5CEE-22CF-4A9A-8194-10A9A55BB283}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8658225" y="1200150"/>
+          <a:ext cx="1039041" cy="432000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MQTT Sub</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>108150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="Rectangle 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E5605B6-444F-4EEC-9ED0-CD0D5F5CAF70}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10495189" y="1200150"/>
+          <a:ext cx="1039042" cy="432000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Patient Response</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1000">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>108149</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="Rectangle 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07DBF833-B136-4035-BE46-CF1031D3BBEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12332154" y="1200149"/>
+          <a:ext cx="1039041" cy="432000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Influx</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> Writer</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>208188</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>198664</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Rectangle 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{132F73B2-AAE8-4DE4-AEB2-871108398D93}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="817788" y="9829800"/>
+          <a:ext cx="4867276" cy="327660"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Fall Event Injection Flow</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="2000" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="42" name="Straight Arrow Connector 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA70B8C7-1BE6-46F2-82F8-4414DF6724CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3702504" y="2905125"/>
+          <a:ext cx="1748517" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="43" name="Straight Arrow Connector 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9131383-A891-4466-BA4A-4D18BA2CEADC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5568043" y="4505325"/>
+          <a:ext cx="1748518" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>388620</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="Rectangle 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3209DED-8042-45E4-BC39-5CD512842CB9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4495800" y="3038475"/>
+          <a:ext cx="2016034" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Data preprocessor</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Resample &gt;</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> lsb/G &gt; last 9sec &gt; features </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="900">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="85000"/>
+                <a:lumOff val="15000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>369570</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="Rectangle 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F374A521-51C6-45E1-A428-29969EC76CFD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4476750" y="3495675"/>
+          <a:ext cx="2016034" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Result</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>confidence</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> &gt; 0.5 = Fall</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="900" b="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="85000"/>
+                <a:lumOff val="15000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="46" name="Straight Arrow Connector 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2E9301B-896A-448D-8A62-C31A241DB2BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7414532" y="5143500"/>
+          <a:ext cx="1748518" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="47" name="Straight Arrow Connector 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3833AD54-D1CA-4155-A271-070B23972AF7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9241971" y="5838825"/>
+          <a:ext cx="1748518" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="48" name="Straight Arrow Connector 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B50F78D0-C79C-401D-AF9A-C7B1F551A788}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9210675" y="16163925"/>
+          <a:ext cx="1743075" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>180974</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="Rectangle 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC1D996D-4055-4C77-9708-F8E1B371D826}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="993321" y="10277475"/>
+          <a:ext cx="1636939" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Mobile</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> App</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="900" b="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>276224</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>323849</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="Rectangle 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C8903F1-F522-4D40-819A-1C5B2FAFE738}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4562474" y="752475"/>
+          <a:ext cx="3721554" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Backend</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>447673</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>200024</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="Rectangle 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1251D49-CA77-4DCA-95EB-BD4C554B2FF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6543673" y="10277475"/>
+          <a:ext cx="5238751" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Mobile</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> App</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="900" b="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="Rectangle 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3222E551-D829-4CD5-AF01-C08DB9F3FB2E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12011025" y="10277475"/>
+          <a:ext cx="1781175" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Backend</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>108149</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="Rectangle 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64BB94E0-B4D8-40F7-AD05-FCB11AA0E3B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11107511" y="10725149"/>
+          <a:ext cx="1039041" cy="432000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Postgres Writer</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>579664</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>417740</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="Rectangle 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC51A78D-1BA3-4F6A-9426-A9349966A3FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16500021" y="10277475"/>
+          <a:ext cx="2287362" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Web</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> App</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="900" b="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="55" name="Straight Arrow Connector 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2620A840-928C-4C91-B6AE-DDDFAAC9682B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3771900" y="4505325"/>
+          <a:ext cx="1600200" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="58" name="Straight Arrow Connector 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1331A532-1520-4320-A108-6DCA1F4A5495}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3771900" y="4505325"/>
+          <a:ext cx="1600200" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2979,4 +9387,2402 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F5F8DD-066E-404B-880B-D3D7B4214C4F}">
+  <dimension ref="E7:AA51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="7" spans="27:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AA7" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="27:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AA9" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E42" s="1"/>
+    </row>
+    <row r="46" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E46" s="1"/>
+    </row>
+    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E51" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AEB2071-28A2-48BB-B77C-31D6CC6F6BEA}">
+  <dimension ref="B2:X98"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+    </row>
+    <row r="3" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+    </row>
+    <row r="4" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+    </row>
+    <row r="5" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+    </row>
+    <row r="6" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+    </row>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
+    </row>
+    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
+    </row>
+    <row r="12" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+    </row>
+    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+    </row>
+    <row r="14" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="9"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
+    </row>
+    <row r="15" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" s="9"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+    </row>
+    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9"/>
+    </row>
+    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
+    </row>
+    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9"/>
+    </row>
+    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9"/>
+    </row>
+    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="9"/>
+    </row>
+    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="9"/>
+    </row>
+    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="10"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+    </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="I23" s="9"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L23" s="9"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="10"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+    </row>
+    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9"/>
+    </row>
+    <row r="25" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="O25" s="9"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="10"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+    </row>
+    <row r="26" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="O26" s="9"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="10"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+    </row>
+    <row r="27" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="10"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="10"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+    </row>
+    <row r="28" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="R28" s="9"/>
+      <c r="S28" s="10"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="10"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+    </row>
+    <row r="29" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="R29" s="9"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="10"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
+    </row>
+    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="R30" s="9"/>
+      <c r="S30" s="10"/>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9"/>
+      <c r="V30" s="10"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
+    </row>
+    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="10"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="10"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+    </row>
+    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
+      <c r="S32" s="10"/>
+      <c r="T32" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="U32" s="9"/>
+      <c r="V32" s="10"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9"/>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="U33" s="9"/>
+      <c r="V33" s="10"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="9"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="9"/>
+      <c r="U34" s="9"/>
+      <c r="V34" s="10"/>
+      <c r="W34" s="9"/>
+      <c r="X34" s="9"/>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
+      <c r="V35" s="10"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9"/>
+    </row>
+    <row r="36" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+      <c r="S36" s="10"/>
+      <c r="T36" s="9"/>
+      <c r="U36" s="9"/>
+      <c r="V36" s="10"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9"/>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
+      <c r="V37" s="10"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9"/>
+    </row>
+    <row r="38" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="10"/>
+      <c r="T38" s="9"/>
+      <c r="U38" s="9"/>
+      <c r="V38" s="10"/>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9"/>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="10"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="10"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="9"/>
+      <c r="S40" s="10"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9"/>
+      <c r="V40" s="10"/>
+      <c r="W40" s="9"/>
+      <c r="X40" s="9"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="10"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
+      <c r="V41" s="10"/>
+      <c r="W41" s="9"/>
+      <c r="X41" s="9"/>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="9"/>
+      <c r="R42" s="9"/>
+      <c r="S42" s="10"/>
+      <c r="T42" s="9"/>
+      <c r="U42" s="9"/>
+      <c r="V42" s="10"/>
+      <c r="W42" s="9"/>
+      <c r="X42" s="9"/>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="9"/>
+      <c r="R43" s="9"/>
+      <c r="S43" s="10"/>
+      <c r="T43" s="9"/>
+      <c r="U43" s="9"/>
+      <c r="V43" s="10"/>
+      <c r="W43" s="9"/>
+      <c r="X43" s="9"/>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="9"/>
+      <c r="O44" s="9"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="9"/>
+      <c r="R44" s="9"/>
+      <c r="S44" s="10"/>
+      <c r="T44" s="9"/>
+      <c r="U44" s="9"/>
+      <c r="V44" s="10"/>
+      <c r="W44" s="9"/>
+      <c r="X44" s="9"/>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="9"/>
+      <c r="O45" s="9"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="9"/>
+      <c r="R45" s="9"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
+      <c r="V45" s="10"/>
+      <c r="W45" s="9"/>
+      <c r="X45" s="9"/>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="9"/>
+      <c r="O46" s="9"/>
+      <c r="P46" s="9"/>
+      <c r="Q46" s="9"/>
+      <c r="R46" s="9"/>
+      <c r="S46" s="9"/>
+      <c r="T46" s="9"/>
+      <c r="U46" s="9"/>
+      <c r="V46" s="9"/>
+      <c r="W46" s="9"/>
+      <c r="X46" s="9"/>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9"/>
+      <c r="O47" s="9"/>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="9"/>
+      <c r="R47" s="9"/>
+      <c r="S47" s="9"/>
+      <c r="T47" s="9"/>
+      <c r="U47" s="9"/>
+      <c r="V47" s="9"/>
+      <c r="W47" s="9"/>
+      <c r="X47" s="9"/>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9"/>
+      <c r="O48" s="9"/>
+      <c r="P48" s="9"/>
+      <c r="Q48" s="9"/>
+      <c r="R48" s="9"/>
+      <c r="S48" s="9"/>
+      <c r="T48" s="9"/>
+      <c r="U48" s="9"/>
+      <c r="V48" s="9"/>
+      <c r="W48" s="9"/>
+      <c r="X48" s="9"/>
+    </row>
+    <row r="52" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="9"/>
+      <c r="K52" s="9"/>
+      <c r="L52" s="9"/>
+      <c r="M52" s="9"/>
+      <c r="N52" s="9"/>
+      <c r="O52" s="9"/>
+      <c r="P52" s="9"/>
+      <c r="Q52" s="9"/>
+      <c r="R52" s="9"/>
+      <c r="S52" s="9"/>
+      <c r="T52" s="9"/>
+      <c r="U52" s="9"/>
+      <c r="V52" s="9"/>
+      <c r="W52" s="9"/>
+    </row>
+    <row r="53" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+      <c r="N53" s="9"/>
+      <c r="O53" s="9"/>
+      <c r="P53" s="9"/>
+      <c r="Q53" s="9"/>
+      <c r="R53" s="9"/>
+      <c r="S53" s="9"/>
+      <c r="T53" s="9"/>
+      <c r="U53" s="9"/>
+      <c r="V53" s="9"/>
+      <c r="W53" s="9"/>
+    </row>
+    <row r="54" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
+      <c r="K54" s="9"/>
+      <c r="L54" s="9"/>
+      <c r="M54" s="9"/>
+      <c r="N54" s="9"/>
+      <c r="O54" s="9"/>
+      <c r="P54" s="9"/>
+      <c r="Q54" s="9"/>
+      <c r="R54" s="9"/>
+      <c r="S54" s="9"/>
+      <c r="T54" s="9"/>
+      <c r="U54" s="9"/>
+      <c r="V54" s="9"/>
+      <c r="W54" s="9"/>
+    </row>
+    <row r="55" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="9"/>
+      <c r="M55" s="9"/>
+      <c r="N55" s="9"/>
+      <c r="O55" s="9"/>
+      <c r="P55" s="9"/>
+      <c r="Q55" s="9"/>
+      <c r="R55" s="9"/>
+      <c r="S55" s="9"/>
+      <c r="T55" s="9"/>
+      <c r="U55" s="9"/>
+      <c r="V55" s="9"/>
+      <c r="W55" s="9"/>
+    </row>
+    <row r="56" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
+      <c r="K56" s="9"/>
+      <c r="L56" s="9"/>
+      <c r="M56" s="9"/>
+      <c r="N56" s="9"/>
+      <c r="O56" s="9"/>
+      <c r="P56" s="9"/>
+      <c r="Q56" s="9"/>
+      <c r="R56" s="9"/>
+      <c r="S56" s="9"/>
+      <c r="T56" s="9"/>
+      <c r="U56" s="9"/>
+      <c r="V56" s="9"/>
+      <c r="W56" s="9"/>
+    </row>
+    <row r="57" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
+      <c r="K57" s="9"/>
+      <c r="L57" s="9"/>
+      <c r="M57" s="9"/>
+      <c r="N57" s="9"/>
+      <c r="O57" s="9"/>
+      <c r="P57" s="9"/>
+      <c r="Q57" s="9"/>
+      <c r="R57" s="9"/>
+      <c r="S57" s="9"/>
+      <c r="T57" s="9"/>
+      <c r="U57" s="9"/>
+      <c r="V57" s="9"/>
+      <c r="W57" s="9"/>
+    </row>
+    <row r="58" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+      <c r="M58" s="9"/>
+      <c r="N58" s="9"/>
+      <c r="O58" s="9"/>
+      <c r="P58" s="9"/>
+      <c r="Q58" s="9"/>
+      <c r="R58" s="9"/>
+      <c r="S58" s="9"/>
+      <c r="T58" s="9"/>
+      <c r="U58" s="9"/>
+      <c r="V58" s="9"/>
+      <c r="W58" s="9"/>
+    </row>
+    <row r="59" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="10"/>
+      <c r="K59" s="9"/>
+      <c r="L59" s="9"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="9"/>
+      <c r="O59" s="9"/>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="9"/>
+      <c r="R59" s="9"/>
+      <c r="S59" s="10"/>
+      <c r="T59" s="12"/>
+      <c r="U59" s="9"/>
+      <c r="V59" s="10"/>
+      <c r="W59" s="9"/>
+    </row>
+    <row r="60" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B60" s="11"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="10"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="10"/>
+      <c r="K60" s="9"/>
+      <c r="L60" s="9"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="9"/>
+      <c r="O60" s="9"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="9"/>
+      <c r="R60" s="9"/>
+      <c r="S60" s="10"/>
+      <c r="T60" s="12"/>
+      <c r="U60" s="9"/>
+      <c r="V60" s="10"/>
+      <c r="W60" s="9"/>
+    </row>
+    <row r="61" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B61" s="11"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="9"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="9"/>
+      <c r="L61" s="9"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="9"/>
+      <c r="O61" s="9"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="9"/>
+      <c r="R61" s="9"/>
+      <c r="S61" s="10"/>
+      <c r="T61" s="12"/>
+      <c r="U61" s="9"/>
+      <c r="V61" s="10"/>
+      <c r="W61" s="9"/>
+    </row>
+    <row r="62" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="9"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="10"/>
+      <c r="K62" s="9"/>
+      <c r="L62" s="9"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="9"/>
+      <c r="O62" s="9"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="9"/>
+      <c r="R62" s="9"/>
+      <c r="S62" s="10"/>
+      <c r="T62" s="12"/>
+      <c r="U62" s="9"/>
+      <c r="V62" s="10"/>
+      <c r="W62" s="9"/>
+    </row>
+    <row r="63" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="10"/>
+      <c r="H63" s="9"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="10"/>
+      <c r="K63" s="9"/>
+      <c r="L63" s="9"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="9"/>
+      <c r="O63" s="9"/>
+      <c r="P63" s="10"/>
+      <c r="Q63" s="9"/>
+      <c r="R63" s="9"/>
+      <c r="S63" s="10"/>
+      <c r="T63" s="12"/>
+      <c r="U63" s="9"/>
+      <c r="V63" s="10"/>
+      <c r="W63" s="9"/>
+    </row>
+    <row r="64" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F64" s="9"/>
+      <c r="G64" s="10"/>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="10"/>
+      <c r="K64" s="9"/>
+      <c r="L64" s="9"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="9"/>
+      <c r="O64" s="9"/>
+      <c r="P64" s="10"/>
+      <c r="Q64" s="9"/>
+      <c r="R64" s="9"/>
+      <c r="S64" s="10"/>
+      <c r="T64" s="12"/>
+      <c r="U64" s="9"/>
+      <c r="V64" s="10"/>
+      <c r="W64" s="9"/>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F65" s="9"/>
+      <c r="G65" s="10"/>
+      <c r="H65" s="9"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="10"/>
+      <c r="K65" s="9"/>
+      <c r="L65" s="9"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="9"/>
+      <c r="O65" s="9"/>
+      <c r="P65" s="10"/>
+      <c r="Q65" s="9"/>
+      <c r="R65" s="9"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="12"/>
+      <c r="U65" s="9"/>
+      <c r="V65" s="10"/>
+      <c r="W65" s="9"/>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="9"/>
+      <c r="I66" s="9"/>
+      <c r="J66" s="10"/>
+      <c r="K66" s="9"/>
+      <c r="L66" s="9"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="9"/>
+      <c r="O66" s="9"/>
+      <c r="P66" s="10"/>
+      <c r="Q66" s="9"/>
+      <c r="R66" s="9"/>
+      <c r="S66" s="10"/>
+      <c r="T66" s="12"/>
+      <c r="U66" s="9"/>
+      <c r="V66" s="10"/>
+      <c r="W66" s="9"/>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="9"/>
+      <c r="I67" s="9"/>
+      <c r="J67" s="10"/>
+      <c r="K67" s="9"/>
+      <c r="L67" s="9"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="9"/>
+      <c r="O67" s="9"/>
+      <c r="P67" s="10"/>
+      <c r="Q67" s="9"/>
+      <c r="R67" s="9"/>
+      <c r="S67" s="10"/>
+      <c r="T67" s="12"/>
+      <c r="U67" s="9"/>
+      <c r="V67" s="10"/>
+      <c r="W67" s="9"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="9"/>
+      <c r="I68" s="9"/>
+      <c r="J68" s="10"/>
+      <c r="K68" s="9"/>
+      <c r="L68" s="9"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="9"/>
+      <c r="O68" s="9"/>
+      <c r="P68" s="10"/>
+      <c r="Q68" s="9"/>
+      <c r="R68" s="9"/>
+      <c r="S68" s="10"/>
+      <c r="T68" s="12"/>
+      <c r="U68" s="9"/>
+      <c r="V68" s="10"/>
+      <c r="W68" s="9"/>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="10"/>
+      <c r="H69" s="9"/>
+      <c r="I69" s="9"/>
+      <c r="J69" s="10"/>
+      <c r="K69" s="9"/>
+      <c r="L69" s="9"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="9"/>
+      <c r="O69" s="9"/>
+      <c r="P69" s="10"/>
+      <c r="Q69" s="9"/>
+      <c r="R69" s="9"/>
+      <c r="S69" s="10"/>
+      <c r="T69" s="12"/>
+      <c r="U69" s="9"/>
+      <c r="V69" s="10"/>
+      <c r="W69" s="9"/>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="10"/>
+      <c r="H70" s="9"/>
+      <c r="I70" s="9"/>
+      <c r="J70" s="10"/>
+      <c r="K70" s="9"/>
+      <c r="L70" s="9"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="9"/>
+      <c r="O70" s="9"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="9"/>
+      <c r="R70" s="9"/>
+      <c r="S70" s="10"/>
+      <c r="T70" s="12"/>
+      <c r="U70" s="9"/>
+      <c r="V70" s="10"/>
+      <c r="W70" s="9"/>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="9"/>
+      <c r="I71" s="9"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="9"/>
+      <c r="L71" s="9"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="9"/>
+      <c r="O71" s="9"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="9"/>
+      <c r="R71" s="9"/>
+      <c r="S71" s="10"/>
+      <c r="T71" s="12"/>
+      <c r="U71" s="9"/>
+      <c r="V71" s="10"/>
+      <c r="W71" s="9"/>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="10"/>
+      <c r="H72" s="9"/>
+      <c r="I72" s="9"/>
+      <c r="J72" s="10"/>
+      <c r="K72" s="9"/>
+      <c r="L72" s="9"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="9"/>
+      <c r="O72" s="9"/>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="9"/>
+      <c r="R72" s="9"/>
+      <c r="S72" s="10"/>
+      <c r="T72" s="12"/>
+      <c r="U72" s="9"/>
+      <c r="V72" s="10"/>
+      <c r="W72" s="9"/>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="10"/>
+      <c r="E73" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F73" s="9"/>
+      <c r="G73" s="10"/>
+      <c r="H73" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I73" s="9"/>
+      <c r="J73" s="10"/>
+      <c r="K73" s="9"/>
+      <c r="L73" s="9"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="9"/>
+      <c r="O73" s="9"/>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="9"/>
+      <c r="R73" s="9"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="12"/>
+      <c r="U73" s="9"/>
+      <c r="V73" s="10"/>
+      <c r="W73" s="9"/>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="9"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="10"/>
+      <c r="H74" s="9"/>
+      <c r="I74" s="9"/>
+      <c r="J74" s="10"/>
+      <c r="K74" s="9"/>
+      <c r="L74" s="9"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="9"/>
+      <c r="O74" s="9"/>
+      <c r="P74" s="10"/>
+      <c r="Q74" s="9"/>
+      <c r="R74" s="9"/>
+      <c r="S74" s="10"/>
+      <c r="T74" s="12"/>
+      <c r="U74" s="9"/>
+      <c r="V74" s="10"/>
+      <c r="W74" s="9"/>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="10"/>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="10"/>
+      <c r="H75" s="9"/>
+      <c r="I75" s="9"/>
+      <c r="J75" s="10"/>
+      <c r="K75" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L75" s="9"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="9"/>
+      <c r="O75" s="9"/>
+      <c r="P75" s="10"/>
+      <c r="Q75" s="9"/>
+      <c r="R75" s="9"/>
+      <c r="S75" s="10"/>
+      <c r="T75" s="12"/>
+      <c r="U75" s="9"/>
+      <c r="V75" s="10"/>
+      <c r="W75" s="9"/>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="9"/>
+      <c r="F76" s="9"/>
+      <c r="G76" s="10"/>
+      <c r="H76" s="9"/>
+      <c r="I76" s="9"/>
+      <c r="J76" s="10"/>
+      <c r="K76" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L76" s="9"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="9"/>
+      <c r="O76" s="9"/>
+      <c r="P76" s="10"/>
+      <c r="Q76" s="9"/>
+      <c r="R76" s="9"/>
+      <c r="S76" s="10"/>
+      <c r="T76" s="12"/>
+      <c r="U76" s="9"/>
+      <c r="V76" s="10"/>
+      <c r="W76" s="9"/>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="10"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="10"/>
+      <c r="H77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="10"/>
+      <c r="K77" s="9"/>
+      <c r="L77" s="9"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="9"/>
+      <c r="O77" s="9"/>
+      <c r="P77" s="10"/>
+      <c r="Q77" s="9"/>
+      <c r="R77" s="9"/>
+      <c r="S77" s="10"/>
+      <c r="T77" s="12"/>
+      <c r="U77" s="9"/>
+      <c r="V77" s="10"/>
+      <c r="W77" s="9"/>
+    </row>
+    <row r="78" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="10"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="10"/>
+      <c r="H78" s="9"/>
+      <c r="I78" s="9"/>
+      <c r="J78" s="10"/>
+      <c r="K78" s="9"/>
+      <c r="L78" s="9"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="O78" s="9"/>
+      <c r="P78" s="10"/>
+      <c r="Q78" s="9"/>
+      <c r="R78" s="9"/>
+      <c r="S78" s="10"/>
+      <c r="T78" s="12"/>
+      <c r="U78" s="9"/>
+      <c r="V78" s="10"/>
+      <c r="W78" s="9"/>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="10"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="10"/>
+      <c r="H79" s="9"/>
+      <c r="I79" s="9"/>
+      <c r="J79" s="10"/>
+      <c r="K79" s="9"/>
+      <c r="L79" s="9"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="O79" s="9"/>
+      <c r="P79" s="10"/>
+      <c r="Q79" s="9"/>
+      <c r="R79" s="9"/>
+      <c r="S79" s="10"/>
+      <c r="T79" s="12"/>
+      <c r="U79" s="9"/>
+      <c r="V79" s="10"/>
+      <c r="W79" s="9"/>
+    </row>
+    <row r="80" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="10"/>
+      <c r="H80" s="9"/>
+      <c r="I80" s="9"/>
+      <c r="J80" s="10"/>
+      <c r="K80" s="9"/>
+      <c r="L80" s="9"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O80" s="9"/>
+      <c r="P80" s="10"/>
+      <c r="Q80" s="9"/>
+      <c r="R80" s="9"/>
+      <c r="S80" s="10"/>
+      <c r="T80" s="12"/>
+      <c r="U80" s="9"/>
+      <c r="V80" s="10"/>
+      <c r="W80" s="9"/>
+    </row>
+    <row r="81" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="10"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9"/>
+      <c r="G81" s="10"/>
+      <c r="H81" s="9"/>
+      <c r="I81" s="9"/>
+      <c r="J81" s="10"/>
+      <c r="K81" s="9"/>
+      <c r="L81" s="9"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="9"/>
+      <c r="O81" s="9"/>
+      <c r="P81" s="10"/>
+      <c r="Q81" s="9"/>
+      <c r="R81" s="9"/>
+      <c r="S81" s="10"/>
+      <c r="T81" s="12"/>
+      <c r="U81" s="9"/>
+      <c r="V81" s="10"/>
+      <c r="W81" s="9"/>
+    </row>
+    <row r="82" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B82" s="9"/>
+      <c r="C82" s="9"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="9"/>
+      <c r="F82" s="9"/>
+      <c r="G82" s="10"/>
+      <c r="H82" s="9"/>
+      <c r="I82" s="9"/>
+      <c r="J82" s="10"/>
+      <c r="K82" s="9"/>
+      <c r="L82" s="9"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="9"/>
+      <c r="O82" s="9"/>
+      <c r="P82" s="10"/>
+      <c r="Q82" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="R82" s="9"/>
+      <c r="S82" s="10"/>
+      <c r="T82" s="12"/>
+      <c r="U82" s="9"/>
+      <c r="V82" s="10"/>
+      <c r="W82" s="9"/>
+    </row>
+    <row r="83" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="10"/>
+      <c r="E83" s="9"/>
+      <c r="F83" s="9"/>
+      <c r="G83" s="10"/>
+      <c r="H83" s="9"/>
+      <c r="I83" s="9"/>
+      <c r="J83" s="10"/>
+      <c r="K83" s="9"/>
+      <c r="L83" s="9"/>
+      <c r="M83" s="10"/>
+      <c r="N83" s="9"/>
+      <c r="O83" s="9"/>
+      <c r="P83" s="10"/>
+      <c r="Q83" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="R83" s="9"/>
+      <c r="S83" s="10"/>
+      <c r="T83" s="12"/>
+      <c r="U83" s="9"/>
+      <c r="V83" s="10"/>
+      <c r="W83" s="9"/>
+    </row>
+    <row r="84" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B84" s="9"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="10"/>
+      <c r="E84" s="9"/>
+      <c r="F84" s="9"/>
+      <c r="G84" s="10"/>
+      <c r="H84" s="9"/>
+      <c r="I84" s="9"/>
+      <c r="J84" s="10"/>
+      <c r="K84" s="9"/>
+      <c r="L84" s="9"/>
+      <c r="M84" s="10"/>
+      <c r="N84" s="9"/>
+      <c r="O84" s="9"/>
+      <c r="P84" s="10"/>
+      <c r="Q84" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="R84" s="9"/>
+      <c r="S84" s="10"/>
+      <c r="T84" s="12"/>
+      <c r="U84" s="9"/>
+      <c r="V84" s="10"/>
+      <c r="W84" s="9"/>
+    </row>
+    <row r="85" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B85" s="9"/>
+      <c r="C85" s="9"/>
+      <c r="D85" s="10"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9"/>
+      <c r="G85" s="10"/>
+      <c r="H85" s="9"/>
+      <c r="I85" s="9"/>
+      <c r="J85" s="10"/>
+      <c r="K85" s="9"/>
+      <c r="L85" s="9"/>
+      <c r="M85" s="10"/>
+      <c r="N85" s="9"/>
+      <c r="O85" s="9"/>
+      <c r="P85" s="10"/>
+      <c r="Q85" s="9"/>
+      <c r="R85" s="9"/>
+      <c r="S85" s="10"/>
+      <c r="T85" s="12"/>
+      <c r="U85" s="9"/>
+      <c r="V85" s="10"/>
+      <c r="W85" s="9"/>
+    </row>
+    <row r="86" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B86" s="9"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="10"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="9"/>
+      <c r="G86" s="10"/>
+      <c r="H86" s="9"/>
+      <c r="I86" s="9"/>
+      <c r="J86" s="10"/>
+      <c r="K86" s="9"/>
+      <c r="L86" s="9"/>
+      <c r="M86" s="10"/>
+      <c r="N86" s="9"/>
+      <c r="O86" s="9"/>
+      <c r="P86" s="10"/>
+      <c r="Q86" s="9"/>
+      <c r="R86" s="9"/>
+      <c r="S86" s="10"/>
+      <c r="T86" s="12"/>
+      <c r="U86" s="9"/>
+      <c r="V86" s="10"/>
+      <c r="W86" s="9"/>
+    </row>
+    <row r="87" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B87" s="9"/>
+      <c r="C87" s="9"/>
+      <c r="D87" s="10"/>
+      <c r="E87" s="9"/>
+      <c r="F87" s="9"/>
+      <c r="G87" s="10"/>
+      <c r="H87" s="9"/>
+      <c r="I87" s="9"/>
+      <c r="J87" s="10"/>
+      <c r="K87" s="9"/>
+      <c r="L87" s="9"/>
+      <c r="M87" s="10"/>
+      <c r="N87" s="9"/>
+      <c r="O87" s="9"/>
+      <c r="P87" s="10"/>
+      <c r="Q87" s="9"/>
+      <c r="R87" s="9"/>
+      <c r="S87" s="10"/>
+      <c r="T87" s="12"/>
+      <c r="U87" s="9"/>
+      <c r="V87" s="10"/>
+      <c r="W87" s="9"/>
+    </row>
+    <row r="88" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B88" s="9"/>
+      <c r="C88" s="9"/>
+      <c r="D88" s="10"/>
+      <c r="E88" s="9"/>
+      <c r="F88" s="9"/>
+      <c r="G88" s="10"/>
+      <c r="H88" s="9"/>
+      <c r="I88" s="9"/>
+      <c r="J88" s="10"/>
+      <c r="K88" s="9"/>
+      <c r="L88" s="9"/>
+      <c r="M88" s="10"/>
+      <c r="N88" s="9"/>
+      <c r="O88" s="9"/>
+      <c r="P88" s="10"/>
+      <c r="Q88" s="9"/>
+      <c r="R88" s="9"/>
+      <c r="S88" s="10"/>
+      <c r="T88" s="12"/>
+      <c r="U88" s="9"/>
+      <c r="V88" s="10"/>
+      <c r="W88" s="9"/>
+    </row>
+    <row r="89" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B89" s="9"/>
+      <c r="C89" s="9"/>
+      <c r="D89" s="10"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9"/>
+      <c r="G89" s="10"/>
+      <c r="H89" s="9"/>
+      <c r="I89" s="9"/>
+      <c r="J89" s="10"/>
+      <c r="K89" s="9"/>
+      <c r="L89" s="9"/>
+      <c r="M89" s="10"/>
+      <c r="N89" s="9"/>
+      <c r="O89" s="9"/>
+      <c r="P89" s="10"/>
+      <c r="Q89" s="9"/>
+      <c r="R89" s="9"/>
+      <c r="S89" s="10"/>
+      <c r="T89" s="12"/>
+      <c r="U89" s="9"/>
+      <c r="V89" s="10"/>
+      <c r="W89" s="9"/>
+    </row>
+    <row r="90" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B90" s="9"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="10"/>
+      <c r="E90" s="9"/>
+      <c r="F90" s="9"/>
+      <c r="G90" s="10"/>
+      <c r="H90" s="9"/>
+      <c r="I90" s="9"/>
+      <c r="J90" s="10"/>
+      <c r="K90" s="9"/>
+      <c r="L90" s="9"/>
+      <c r="M90" s="10"/>
+      <c r="N90" s="9"/>
+      <c r="O90" s="9"/>
+      <c r="P90" s="10"/>
+      <c r="Q90" s="9"/>
+      <c r="R90" s="9"/>
+      <c r="S90" s="10"/>
+      <c r="T90" s="12"/>
+      <c r="U90" s="9"/>
+      <c r="V90" s="10"/>
+      <c r="W90" s="9"/>
+    </row>
+    <row r="91" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B91" s="9"/>
+      <c r="C91" s="9"/>
+      <c r="D91" s="10"/>
+      <c r="E91" s="9"/>
+      <c r="F91" s="9"/>
+      <c r="G91" s="10"/>
+      <c r="H91" s="9"/>
+      <c r="I91" s="9"/>
+      <c r="J91" s="10"/>
+      <c r="K91" s="9"/>
+      <c r="L91" s="9"/>
+      <c r="M91" s="10"/>
+      <c r="N91" s="9"/>
+      <c r="O91" s="9"/>
+      <c r="P91" s="10"/>
+      <c r="Q91" s="9"/>
+      <c r="R91" s="9"/>
+      <c r="S91" s="10"/>
+      <c r="T91" s="12"/>
+      <c r="U91" s="9"/>
+      <c r="V91" s="10"/>
+      <c r="W91" s="9"/>
+    </row>
+    <row r="92" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B92" s="9"/>
+      <c r="C92" s="9"/>
+      <c r="D92" s="10"/>
+      <c r="E92" s="9"/>
+      <c r="F92" s="9"/>
+      <c r="G92" s="10"/>
+      <c r="H92" s="9"/>
+      <c r="I92" s="9"/>
+      <c r="J92" s="10"/>
+      <c r="K92" s="9"/>
+      <c r="L92" s="9"/>
+      <c r="M92" s="10"/>
+      <c r="N92" s="9"/>
+      <c r="O92" s="9"/>
+      <c r="P92" s="10"/>
+      <c r="Q92" s="9"/>
+      <c r="R92" s="9"/>
+      <c r="S92" s="10"/>
+      <c r="T92" s="12"/>
+      <c r="U92" s="9"/>
+      <c r="V92" s="10"/>
+      <c r="W92" s="9"/>
+    </row>
+    <row r="93" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B93" s="9"/>
+      <c r="C93" s="9"/>
+      <c r="D93" s="10"/>
+      <c r="E93" s="9"/>
+      <c r="F93" s="9"/>
+      <c r="G93" s="10"/>
+      <c r="H93" s="9"/>
+      <c r="I93" s="9"/>
+      <c r="J93" s="10"/>
+      <c r="K93" s="9"/>
+      <c r="L93" s="9"/>
+      <c r="M93" s="10"/>
+      <c r="N93" s="9"/>
+      <c r="O93" s="9"/>
+      <c r="P93" s="10"/>
+      <c r="Q93" s="9"/>
+      <c r="R93" s="9"/>
+      <c r="S93" s="10"/>
+      <c r="T93" s="12"/>
+      <c r="U93" s="9"/>
+      <c r="V93" s="10"/>
+      <c r="W93" s="9"/>
+    </row>
+    <row r="94" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B94" s="9"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="10"/>
+      <c r="E94" s="9"/>
+      <c r="F94" s="9"/>
+      <c r="G94" s="10"/>
+      <c r="H94" s="9"/>
+      <c r="I94" s="9"/>
+      <c r="J94" s="10"/>
+      <c r="K94" s="9"/>
+      <c r="L94" s="9"/>
+      <c r="M94" s="10"/>
+      <c r="N94" s="9"/>
+      <c r="O94" s="9"/>
+      <c r="P94" s="10"/>
+      <c r="Q94" s="9"/>
+      <c r="R94" s="9"/>
+      <c r="S94" s="10"/>
+      <c r="T94" s="12"/>
+      <c r="U94" s="9"/>
+      <c r="V94" s="10"/>
+      <c r="W94" s="9"/>
+    </row>
+    <row r="95" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="10"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="10"/>
+      <c r="H95" s="9"/>
+      <c r="I95" s="9"/>
+      <c r="J95" s="10"/>
+      <c r="K95" s="9"/>
+      <c r="L95" s="9"/>
+      <c r="M95" s="10"/>
+      <c r="N95" s="9"/>
+      <c r="O95" s="9"/>
+      <c r="P95" s="10"/>
+      <c r="Q95" s="9"/>
+      <c r="R95" s="9"/>
+      <c r="S95" s="10"/>
+      <c r="T95" s="12"/>
+      <c r="U95" s="9"/>
+      <c r="V95" s="10"/>
+      <c r="W95" s="9"/>
+    </row>
+    <row r="96" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B96" s="9"/>
+      <c r="C96" s="9"/>
+      <c r="D96" s="9"/>
+      <c r="E96" s="9"/>
+      <c r="F96" s="9"/>
+      <c r="G96" s="9"/>
+      <c r="H96" s="9"/>
+      <c r="I96" s="9"/>
+      <c r="J96" s="9"/>
+      <c r="K96" s="9"/>
+      <c r="L96" s="9"/>
+      <c r="M96" s="9"/>
+      <c r="N96" s="9"/>
+      <c r="O96" s="9"/>
+      <c r="P96" s="9"/>
+      <c r="Q96" s="9"/>
+      <c r="R96" s="9"/>
+      <c r="S96" s="9"/>
+      <c r="T96" s="9"/>
+      <c r="U96" s="9"/>
+      <c r="V96" s="9"/>
+      <c r="W96" s="9"/>
+    </row>
+    <row r="97" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B97" s="9"/>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="9"/>
+      <c r="F97" s="9"/>
+      <c r="G97" s="9"/>
+      <c r="H97" s="9"/>
+      <c r="I97" s="9"/>
+      <c r="J97" s="9"/>
+      <c r="K97" s="9"/>
+      <c r="L97" s="9"/>
+      <c r="M97" s="9"/>
+      <c r="N97" s="9"/>
+      <c r="O97" s="9"/>
+      <c r="P97" s="9"/>
+      <c r="Q97" s="9"/>
+      <c r="R97" s="9"/>
+      <c r="S97" s="9"/>
+      <c r="T97" s="9"/>
+      <c r="U97" s="9"/>
+      <c r="V97" s="9"/>
+      <c r="W97" s="9"/>
+    </row>
+    <row r="98" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B98" s="9"/>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="9"/>
+      <c r="F98" s="9"/>
+      <c r="G98" s="9"/>
+      <c r="H98" s="9"/>
+      <c r="I98" s="9"/>
+      <c r="J98" s="9"/>
+      <c r="K98" s="9"/>
+      <c r="L98" s="9"/>
+      <c r="M98" s="9"/>
+      <c r="N98" s="9"/>
+      <c r="O98" s="9"/>
+      <c r="P98" s="9"/>
+      <c r="Q98" s="9"/>
+      <c r="R98" s="9"/>
+      <c r="S98" s="9"/>
+      <c r="T98" s="9"/>
+      <c r="U98" s="9"/>
+      <c r="V98" s="9"/>
+      <c r="W98" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/_concept_6G_integration/MCS_Fall_Detection.xlsx
+++ b/_concept_6G_integration/MCS_Fall_Detection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hayat\Documents\6G\FallDetection_new\_concept_6G_integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BC606B-2BFB-4C51-8CFF-EE3FC3843CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28CDA26-6BD0-468B-AFD5-B1AD770E0064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="-2970" windowWidth="23232" windowHeight="13872" activeTab="2" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
+    <workbookView xWindow="20544" yWindow="-2970" windowWidth="23232" windowHeight="13872" activeTab="3" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -675,12 +675,12 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4937,15 +4937,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>405541</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>35411</xdr:rowOff>
+      <xdr:colOff>232634</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>57824</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>217618</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>111611</xdr:rowOff>
+      <xdr:colOff>44711</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>134023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4960,8 +4960,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5282341" y="6344771"/>
-          <a:ext cx="1031277" cy="647700"/>
+          <a:off x="5109434" y="6324153"/>
+          <a:ext cx="1031277" cy="654423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5002,18 +5002,18 @@
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>Grafana &amp; Prometeheus</a:t>
+            <a:t>Grafana </a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-GB" sz="900" baseline="0">
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>(Ml performance)</a:t>
+            <a:t>:3000</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -5116,6 +5116,17 @@
               </a:solidFill>
             </a:rPr>
             <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:5432</a:t>
           </a:r>
           <a:endParaRPr lang="en-DE" sz="1100">
             <a:solidFill>
@@ -5196,6 +5207,17 @@
               </a:solidFill>
             </a:rPr>
             <a:t>MLFlow</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:5000</a:t>
           </a:r>
           <a:endParaRPr lang="en-DE" sz="1200">
             <a:solidFill>
@@ -5546,7 +5568,18 @@
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>API</a:t>
+            <a:t>API server</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:8001</a:t>
           </a:r>
           <a:endParaRPr lang="en-DE" sz="1200">
             <a:solidFill>
@@ -5636,6 +5669,17 @@
             </a:rPr>
             <a:t> Broker</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:1883</a:t>
+          </a:r>
           <a:endParaRPr lang="en-DE" sz="1200">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
@@ -5648,16 +5692,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>19691</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>94866</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>185539</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>25053</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>444506</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>171066</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>4564</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>101253</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5672,8 +5716,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4896491" y="4415854"/>
-          <a:ext cx="1034415" cy="654424"/>
+          <a:off x="14815939" y="9953465"/>
+          <a:ext cx="1038225" cy="654423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6925,6 +6969,21 @@
             </a:rPr>
             <a:t>Dashboard backend</a:t>
           </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:8002</a:t>
+          </a:r>
           <a:endParaRPr lang="en-GB" sz="800" baseline="0">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
@@ -7350,11 +7409,108 @@
             </a:rPr>
             <a:t>)</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:5432</a:t>
+          </a:r>
           <a:endParaRPr lang="en-DE" sz="1100">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
             </a:solidFill>
           </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>214704</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>84717</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>32496</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>160916</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="77" name="Rectangle 76">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E6DD959-4E17-4FCC-B702-14DE2252E107}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5091504" y="7122011"/>
+          <a:ext cx="1036992" cy="654423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Prometeheus</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:9090</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7822,7 +7978,7 @@
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>Caregiver</a:t>
+            <a:t>Fall</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-GB" sz="1000" baseline="0">
@@ -17871,19 +18027,19 @@
     </row>
     <row r="6" spans="18:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="X6" s="8"/>
-      <c r="Y6" s="25" t="s">
+      <c r="Y6" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="Z6" s="25"/>
-      <c r="AA6" s="25" t="s">
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="AB6" s="25"/>
-      <c r="AC6" s="25"/>
-      <c r="AD6" s="26"/>
-      <c r="AE6" s="26"/>
-      <c r="AF6" s="26"/>
-      <c r="AG6" s="28" t="s">
+      <c r="AB6" s="29"/>
+      <c r="AC6" s="29"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="27" t="s">
         <v>91</v>
       </c>
       <c r="AH6" s="16"/>
@@ -17891,15 +18047,15 @@
     </row>
     <row r="7" spans="18:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="X7" s="8"/>
-      <c r="Y7" s="27"/>
-      <c r="Z7" s="27"/>
-      <c r="AA7" s="27"/>
-      <c r="AB7" s="27"/>
-      <c r="AC7" s="27"/>
-      <c r="AD7" s="27"/>
-      <c r="AE7" s="27"/>
-      <c r="AF7" s="27"/>
-      <c r="AG7" s="27"/>
+      <c r="Y7" s="26"/>
+      <c r="Z7" s="26"/>
+      <c r="AA7" s="26"/>
+      <c r="AB7" s="26"/>
+      <c r="AC7" s="26"/>
+      <c r="AD7" s="26"/>
+      <c r="AE7" s="26"/>
+      <c r="AF7" s="26"/>
+      <c r="AG7" s="26"/>
       <c r="AH7" s="8"/>
       <c r="AI7" s="8"/>
     </row>
@@ -18056,7 +18212,7 @@
       <c r="AD16" s="8"/>
       <c r="AE16" s="8"/>
       <c r="AF16" s="8"/>
-      <c r="AG16" s="29" t="s">
+      <c r="AG16" s="28" t="s">
         <v>96</v>
       </c>
       <c r="AH16" s="8"/>
@@ -18074,7 +18230,7 @@
       <c r="AD17" s="8"/>
       <c r="AE17" s="8"/>
       <c r="AF17" s="8"/>
-      <c r="AG17" s="29" t="s">
+      <c r="AG17" s="28" t="s">
         <v>95</v>
       </c>
       <c r="AH17" s="8"/>
@@ -18092,7 +18248,7 @@
       <c r="AD18" s="8"/>
       <c r="AE18" s="8"/>
       <c r="AF18" s="8"/>
-      <c r="AG18" s="29" t="s">
+      <c r="AG18" s="28" t="s">
         <v>95</v>
       </c>
       <c r="AH18" s="8"/>
@@ -18244,7 +18400,7 @@
       <c r="AD28" s="8"/>
       <c r="AE28" s="8"/>
       <c r="AF28" s="8"/>
-      <c r="AG28" s="29" t="s">
+      <c r="AG28" s="28" t="s">
         <v>99</v>
       </c>
       <c r="AH28" s="8"/>
@@ -18262,7 +18418,7 @@
       <c r="AD29" s="8"/>
       <c r="AE29" s="8"/>
       <c r="AF29" s="8"/>
-      <c r="AG29" s="29" t="s">
+      <c r="AG29" s="28" t="s">
         <v>99</v>
       </c>
       <c r="AH29" s="8"/>
@@ -18280,7 +18436,7 @@
       <c r="AD30" s="8"/>
       <c r="AE30" s="8"/>
       <c r="AF30" s="8"/>
-      <c r="AG30" s="29" t="s">
+      <c r="AG30" s="28" t="s">
         <v>99</v>
       </c>
       <c r="AH30" s="8"/>
@@ -18298,7 +18454,7 @@
       <c r="AD31" s="8"/>
       <c r="AE31" s="8"/>
       <c r="AF31" s="8"/>
-      <c r="AG31" s="29" t="s">
+      <c r="AG31" s="28" t="s">
         <v>99</v>
       </c>
       <c r="AH31" s="8"/>
@@ -18316,7 +18472,7 @@
       <c r="AD32" s="8"/>
       <c r="AE32" s="8"/>
       <c r="AF32" s="8"/>
-      <c r="AG32" s="29" t="s">
+      <c r="AG32" s="28" t="s">
         <v>99</v>
       </c>
       <c r="AH32" s="8"/>

--- a/_concept_6G_integration/MCS_Fall_Detection.xlsx
+++ b/_concept_6G_integration/MCS_Fall_Detection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hayat\Documents\6G\FallDetection_new\_concept_6G_integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28CDA26-6BD0-468B-AFD5-B1AD770E0064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE1DE29-E6B3-469E-8F3F-5AE37890C4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="-2970" windowWidth="23232" windowHeight="13872" activeTab="3" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
+    <workbookView xWindow="20544" yWindow="-2970" windowWidth="23232" windowHeight="13872" activeTab="2" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="109">
   <si>
     <t>1.</t>
   </si>
@@ -426,13 +426,16 @@
     <t>to avoid latecy to the mob app</t>
   </si>
   <si>
-    <t xml:space="preserve">Writes the </t>
+    <t>Writes Inference_log table</t>
   </si>
   <si>
-    <t>confidence, model_version, timestamp</t>
+    <t>Obsrv_id, pat_id, dev_id, model_ver</t>
   </si>
   <si>
-    <t>wha</t>
+    <t>fall_detected, confidence, timestamp, latency etc.</t>
+  </si>
+  <si>
+    <t>SSE</t>
   </si>
 </sst>
 </file>
@@ -630,7 +633,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -679,6 +682,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2757,15 +2763,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>186690</xdr:colOff>
+      <xdr:colOff>219299</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>112060</xdr:rowOff>
+      <xdr:rowOff>94130</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>321129</xdr:colOff>
+      <xdr:colOff>353738</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>186692</xdr:rowOff>
+      <xdr:rowOff>168762</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2780,8 +2786,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1405890" y="3854825"/>
-          <a:ext cx="11107239" cy="4700420"/>
+          <a:off x="1438499" y="3827930"/>
+          <a:ext cx="11107239" cy="4646632"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3052,149 +3058,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>387612</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>6724</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>202827</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>86733</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Rectangle 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{023D984C-2B84-43A7-AFC1-1A409F328018}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5874012" y="5291418"/>
-          <a:ext cx="1034415" cy="658233"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>InfluxDB</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1200">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>109482</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>129539</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>390254</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>17929</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Rectangle 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D70B74BF-EB61-409C-AF90-3089426F7ABC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4376682" y="4275715"/>
-          <a:ext cx="7595972" cy="3935955"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:prstDash val="dash"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="en-DE" sz="1200">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>29963</xdr:colOff>
       <xdr:row>20</xdr:row>
@@ -3615,15 +3478,7 @@
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>Web App / Front</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> end</a:t>
+            <a:t>Web App / Browser</a:t>
           </a:r>
           <a:endParaRPr lang="en-DE" sz="1200">
             <a:solidFill>
@@ -3810,7 +3665,7 @@
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>Dashboard</a:t>
+            <a:t>Pat Dashboard</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3971,84 +3826,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>216705</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>44900</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>21516</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>94429</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="Rectangle 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB87A18F-B73D-423F-9977-8238C491F58B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7531905" y="4365888"/>
-          <a:ext cx="2243211" cy="242270"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="002060"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Changeable Component</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1200">
-            <a:solidFill>
-              <a:srgbClr val="002060"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>168380</xdr:colOff>
       <xdr:row>47</xdr:row>
@@ -4442,7 +4219,7 @@
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>Dashboard</a:t>
+            <a:t>Fall Dashboard</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -4461,7 +4238,7 @@
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t> history</a:t>
+            <a:t> history + alert</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-GB" sz="1000">
@@ -4573,6 +4350,7 @@
           <a:solidFill>
             <a:schemeClr val="tx1"/>
           </a:solidFill>
+          <a:headEnd type="triangle"/>
           <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
@@ -4629,6 +4407,7 @@
           <a:solidFill>
             <a:schemeClr val="tx1"/>
           </a:solidFill>
+          <a:headEnd type="triangle"/>
           <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
@@ -4855,16 +4634,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>244849</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>129443</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>508315</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>130629</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>244929</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>125506</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>87086</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>128644</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4879,8 +4658,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5121649" y="6203031"/>
-          <a:ext cx="4267280" cy="1730734"/>
+          <a:off x="7213915" y="6340929"/>
+          <a:ext cx="3845971" cy="1712515"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4936,16 +4715,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>232634</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>57824</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>94609</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>4019</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>44711</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>134023</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>514381</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>77977</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4960,8 +4739,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5109434" y="6324153"/>
-          <a:ext cx="1031277" cy="654423"/>
+          <a:off x="7409809" y="6404819"/>
+          <a:ext cx="1029372" cy="645458"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5022,23 +4801,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>555091</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>161829</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>102198</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>70149</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>369633</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>47529</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>521970</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>148253</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="Rectangle 33">
+        <xdr:cNvPr id="51" name="Rectangle 50">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB419F36-7831-4631-AD43-8C71165FF4DC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9892203A-BA7F-4DFD-8345-84DF7E0F7AD3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5046,8 +4825,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7870291" y="6279600"/>
-          <a:ext cx="1033742" cy="647700"/>
+          <a:off x="8636598" y="7300184"/>
+          <a:ext cx="1029372" cy="656328"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5088,124 +4867,6 @@
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>Postgres</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1050">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Fall_detection</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>:5432</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>533176</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>14456</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>345253</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>90656</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="51" name="Rectangle 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9892203A-BA7F-4DFD-8345-84DF7E0F7AD3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6629176" y="6323816"/>
-          <a:ext cx="1031277" cy="647700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="002060"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="002060"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
             <a:t>MLFlow</a:t>
           </a:r>
         </a:p>
@@ -5232,15 +4893,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>36388</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>175163</xdr:rowOff>
+      <xdr:colOff>436583</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>167096</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>372020</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>78105</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>168330</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5255,8 +4916,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9789988" y="4959434"/>
-          <a:ext cx="1554832" cy="2188942"/>
+          <a:off x="10190183" y="4662896"/>
+          <a:ext cx="1560547" cy="1465761"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5301,386 +4962,6 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:endParaRPr lang="en-DE" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>480172</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>183795</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>293481</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>69158</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="Rectangle 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D97889AF-DA54-4A0E-AB55-FF0B0E7A031A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7185772" y="5275748"/>
-          <a:ext cx="1032509" cy="656328"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="002060"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Data Preprocessor</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1200">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>287655</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>96338</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>97155</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>172538</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="Rectangle 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{616B7331-EA63-41E0-8CA9-9E41D019BF60}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10041255" y="6214109"/>
-          <a:ext cx="1028700" cy="647700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="002060"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="002060"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>MQTT</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> Client 2</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1050" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(alert displayer)</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1050">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>442712</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>5381</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>256021</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>81580</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="Rectangle 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FAD7A48-165B-40A3-A589-E5A337D4C822}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8367512" y="5290075"/>
-          <a:ext cx="1032509" cy="654423"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="002060"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="002060"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Inference</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>API server</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>:8001</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1200">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>277313</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>114844</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>86813</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>544</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="50" name="Rectangle 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76919A6E-6E83-4784-90EF-97F27C233BE8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10030913" y="5280115"/>
-          <a:ext cx="1028700" cy="647700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="002060"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="002060"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>MQTT</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> Broker</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>:1883</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1200">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
             </a:solidFill>
@@ -6745,353 +6026,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>473672</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>185809</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>78472</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>52669</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>286982</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>71510</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="Rectangle 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84703822-5F99-470D-AEB5-B0949F0422C9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2302472" y="4892280"/>
-          <a:ext cx="1032510" cy="656665"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>FHIR</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> DB</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1200">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>580128</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>110490</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>201705</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>148443</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="Rectangle 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C70BC7D-D097-4E84-9430-A21552E3AAD3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1799328" y="4238737"/>
-          <a:ext cx="2059977" cy="3314553"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="bg1">
-              <a:lumMod val="75000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="dash"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="en-DE" sz="1200">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>504504</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>189482</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>303454</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>56425</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="72" name="Rectangle 71">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63B17D3D-D374-4205-80CD-24266A83C401}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3552504" y="6437882"/>
-          <a:ext cx="1018150" cy="637908"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="002060"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Dashboard backend</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>:8002</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-GB" sz="800" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>558292</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>167071</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>361052</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>34014</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="21" name="Rectangle 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DF8F53B-0B98-427A-BA5B-0B5E2CD748A9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3606292" y="5644506"/>
-          <a:ext cx="1021960" cy="637908"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="002060"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Data fetcher</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(for current dashboard)</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>108585</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>138169</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>530262</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>498244</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>21629</xdr:rowOff>
+      <xdr:rowOff>128870</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7106,8 +6050,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6204585" y="7175463"/>
-          <a:ext cx="1031277" cy="654425"/>
+          <a:off x="9832072" y="7215469"/>
+          <a:ext cx="1029372" cy="647701"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7314,16 +6258,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>599915</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>145164</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>191348</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>63809</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>420172</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>28959</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>9700</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>140346</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7338,8 +6282,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7305515" y="7182458"/>
-          <a:ext cx="1039457" cy="654760"/>
+          <a:off x="8725748" y="6522880"/>
+          <a:ext cx="1037552" cy="654760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7432,16 +6376,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>214704</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>84717</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>66114</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>7845</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>32496</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>160916</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>491601</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>84044</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7456,8 +6400,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5091504" y="7122011"/>
-          <a:ext cx="1036992" cy="654423"/>
+          <a:off x="7381314" y="7237880"/>
+          <a:ext cx="1035087" cy="654423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7516,11 +6460,1734 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>20732</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>445658</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>28798</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Rectangle 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4AAFE0D-0416-44FE-9662-765A330E3412}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5507132" y="4762499"/>
+          <a:ext cx="1644126" cy="3191099"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="10000"/>
+            <a:lumOff val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>244176</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>36546</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>515471</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Rectangle 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E31A638-4D14-42B6-86ED-BD4671D3EC00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2072976" y="4760946"/>
+          <a:ext cx="3319295" cy="2738030"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="10000"/>
+            <a:lumOff val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>260488</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>183105</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>276561</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>144124</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Rectangle 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB419F36-7831-4631-AD43-8C71165FF4DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5746888" y="5100246"/>
+          <a:ext cx="1235273" cy="731984"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Postgres</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="700" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>inference_log + fall_history</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:5432</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>104183</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>189810</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>523283</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>75511</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Rectangle 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{616B7331-EA63-41E0-8CA9-9E41D019BF60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10467383" y="5447610"/>
+          <a:ext cx="1028700" cy="647701"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MQTT</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> Client 2</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(alert displayer)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>131285</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>26142</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>550385</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>104583</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="Rectangle 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76919A6E-6E83-4784-90EF-97F27C233BE8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10494485" y="4712442"/>
+          <a:ext cx="1028700" cy="649941"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MQTT</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> Broker</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:1883</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>350086</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>125384</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>145226</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>5715</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="72" name="Rectangle 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63B17D3D-D374-4205-80CD-24266A83C401}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5836486" y="6969937"/>
+          <a:ext cx="1014340" cy="844037"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>fall</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>dashboard </a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:8002</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="800" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>346274</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>162474</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>381559</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>27512</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Rectangle 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DF8F53B-0B98-427A-BA5B-0B5E2CD748A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4003874" y="5657839"/>
+          <a:ext cx="1254485" cy="636002"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Pat Dahboard backgroundTasks</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(data fecther etc.) </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1200" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>106119</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>185809</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>529029</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>71510</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Rectangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84703822-5F99-470D-AEB5-B0949F0422C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2544519" y="5102950"/>
+          <a:ext cx="1032510" cy="656666"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FHIR</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> DB</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>580128</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>110490</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>201705</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>148443</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Rectangle 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C70BC7D-D097-4E84-9430-A21552E3AAD3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1799328" y="4238737"/>
+          <a:ext cx="2059977" cy="3314553"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>20968</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>51089</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>425708</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>116541</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Rectangle 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EBAE1B7-951D-DA71-51C8-4CAE44E5DF36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2459368" y="6124677"/>
+          <a:ext cx="1014340" cy="836417"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Patient</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>dashboard </a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:????</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="800" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>295835</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>129539</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>392159</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>17929</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangle 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D70B74BF-EB61-409C-AF90-3089426F7ABC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3953435" y="4275715"/>
+          <a:ext cx="8021124" cy="3935955"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="dash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>227156</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>20944</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>260536</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>78722</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Rectangle 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05717A59-0580-42A6-93BE-7D7A1AF5AC40}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5713556" y="6094532"/>
+          <a:ext cx="1252580" cy="636002"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>fall Dahboard backgroundTasks</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(data fecther etc.) </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1200" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>537882</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>156881</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>277233</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>165847</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Rectangle 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D7194F6-19ED-4908-B972-B9BCAC4EF649}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7243482" y="4688540"/>
+          <a:ext cx="2787351" cy="1550895"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="10000"/>
+            <a:lumOff val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>589733</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>23400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>165190</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>70756</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Rectangle 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB87A18F-B73D-423F-9977-8238C491F58B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4247333" y="4328700"/>
+          <a:ext cx="7500257" cy="237856"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Changeable Component</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:srgbClr val="002060"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>317129</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>86735</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>130439</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>166743</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rectangle 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{023D984C-2B84-43A7-AFC1-1A409F328018}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8851529" y="4811135"/>
+          <a:ext cx="1032510" cy="658232"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>InfluxDB</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>6948</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>80028</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>429857</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>158132</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Rectangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D97889AF-DA54-4A0E-AB55-FF0B0E7A031A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7322148" y="4804428"/>
+          <a:ext cx="1032509" cy="656328"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Data Preprocessor</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>27087</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18157</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>451901</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>94356</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="Rectangle 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FAD7A48-165B-40A3-A589-E5A337D4C822}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7951887" y="5513522"/>
+          <a:ext cx="1034414" cy="654422"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Inference</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>API server</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:8001</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>499141</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>66482</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>321704</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>46196</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Rectangle 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45D33074-E4A0-EFB9-8175-A845D9761FDC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7204741" y="22038976"/>
+          <a:ext cx="7137763" cy="557938"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Mobile app direclty writes</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Fall confirmed @ HH:MM:SSS </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>/</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Help requested @ HH:MM:SSS </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>/</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>No Reponse @ HH:MM:SSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050" b="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="85000"/>
+                <a:lumOff val="15000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -10723,89 +11390,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>57149</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>512445</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>108149</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="165" name="Rectangle 164">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E965EE4E-0D44-48EE-A5D1-F6F76521807C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15937230" y="1200149"/>
-          <a:ext cx="1034415" cy="433905"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1000">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Caregiver</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> DB</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>142874</xdr:colOff>
       <xdr:row>60</xdr:row>
@@ -11183,14 +11767,14 @@
     <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>56606</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>31024</xdr:rowOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>117437</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>569868</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>31024</xdr:rowOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>117437</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -11205,7 +11789,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12858206" y="7843429"/>
+          <a:off x="12858206" y="19357937"/>
           <a:ext cx="513262" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -11246,16 +11830,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>54429</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>111849</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>38373</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>150189</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>527957</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>111849</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>150189</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -11269,9 +11853,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14684829" y="8303349"/>
-          <a:ext cx="1694633" cy="0"/>
+        <a:xfrm flipH="1">
+          <a:off x="16497573" y="19200189"/>
+          <a:ext cx="1790427" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -11578,13 +12162,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>484414</xdr:colOff>
+      <xdr:colOff>268605</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>182880</xdr:rowOff>
+      <xdr:rowOff>186690</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>201931</xdr:colOff>
+      <xdr:colOff>185057</xdr:colOff>
       <xdr:row>64</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
@@ -11601,8 +12185,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13897519" y="756285"/>
-          <a:ext cx="3375117" cy="367665"/>
+          <a:off x="13679805" y="11997690"/>
+          <a:ext cx="3574052" cy="365760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11737,13 +12321,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>49529</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>96066</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>511629</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>96066</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -11879,14 +12463,14 @@
     <xdr:from>
       <xdr:col>22</xdr:col>
       <xdr:colOff>60688</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>171722</xdr:rowOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>63489</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>1905</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>37937</xdr:rowOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>120540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -11901,8 +12485,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13471888" y="7601222"/>
-          <a:ext cx="550817" cy="437715"/>
+          <a:off x="13471888" y="19113489"/>
+          <a:ext cx="550817" cy="438051"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12121,15 +12705,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>63954</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>32929</xdr:rowOff>
+      <xdr:colOff>67764</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>119342</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>575311</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>32929</xdr:rowOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>119342</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -12144,8 +12728,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14086659" y="7845334"/>
-          <a:ext cx="509452" cy="0"/>
+          <a:off x="14088564" y="19359842"/>
+          <a:ext cx="507547" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -12186,15 +12770,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>205468</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>85997</xdr:rowOff>
+      <xdr:colOff>189140</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>87902</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>529046</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>85997</xdr:rowOff>
+      <xdr:colOff>512718</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>87902</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -12209,7 +12793,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11178268" y="7517402"/>
+          <a:off x="11161940" y="19137902"/>
           <a:ext cx="1542778" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -12323,71 +12907,6 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>53341</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>167641</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>538843</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>167641</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="187" name="Straight Arrow Connector 186">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E97DBED-A633-408E-829B-CB4A38AE87DB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7368541" y="17884141"/>
-          <a:ext cx="3533502" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="25400">
-          <a:solidFill>
-            <a:schemeClr val="bg1">
-              <a:lumMod val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-            <a:prstClr val="black">
-              <a:alpha val="40000"/>
-            </a:prstClr>
-          </a:outerShdw>
-        </a:effectLst>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -12638,29 +13157,172 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
-                </a:schemeClr>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Trigger messenger</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1050" b="0">
+            <a:t>Trigger messenger   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-   1.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Did you fall? (T/F),</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>  2.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Do you need help? (T/F) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>or</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>else</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>send help (if no answer after 10sec)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="85000"/>
-                <a:lumOff val="15000"/>
-              </a:schemeClr>
+              <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
+            <a:effectLst/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -12671,13 +13333,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>51236</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>31024</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>566057</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>14548</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -12888,16 +13550,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>79427</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>127699</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>450124</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>20138</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>460082</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>108982</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>117455</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>140278</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -12912,8 +13574,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7394627" y="17281664"/>
-          <a:ext cx="3428655" cy="559506"/>
+          <a:off x="9594124" y="17165138"/>
+          <a:ext cx="2715331" cy="310640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12923,8 +13585,13 @@
             <a:lumMod val="95000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:ln>
-          <a:noFill/>
+        <a:ln w="6350">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -12949,71 +13616,36 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-GB" sz="1050" b="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Did you fall? (T/F)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB">
+            </a:rPr>
+            <a:t>if</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050" b="0" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>  / </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:t> no_answer &gt; 10sec  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050" b="1" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Do you need help? (T/F) /</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB">
+            </a:rPr>
+            <a:t>or</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050" b="0" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-GB">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>send help (if no answer after 10sec)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
+            <a:t>   help_needed = T</a:t>
           </a:r>
           <a:endParaRPr lang="en-DE" sz="1050" b="0">
             <a:solidFill>
@@ -13157,91 +13789,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>57149</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>107225</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>111306</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>512445</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>108149</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="200" name="Rectangle 199">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC3154FF-77A8-4475-A83B-72AC065E8D61}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="18375630" y="12439649"/>
-          <a:ext cx="1034415" cy="433905"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1000">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Writer</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>424232</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>107833</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>195287</xdr:colOff>
-      <xdr:row>113</xdr:row>
-      <xdr:rowOff>89116</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>582386</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>85453</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -13256,8 +13813,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14445032" y="21062833"/>
-          <a:ext cx="3428655" cy="552783"/>
+          <a:off x="14737625" y="17827806"/>
+          <a:ext cx="1694361" cy="545647"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -13295,73 +13852,531 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Did you fall? (T/F)</a:t>
+            <a:t>Alert message</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-GB">
               <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>  / </a:t>
-          </a:r>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Do you need help? (T/F) /</a:t>
+            <a:t>Patient XX fell, needs help</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-GB">
               <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
               </a:solidFill>
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:br>
-            <a:rPr lang="en-GB">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
+          <a:endParaRPr lang="en-DE" sz="1050" b="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="85000"/>
+                <a:lumOff val="15000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>52524</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>11221</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>566681</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>11221</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Straight Arrow Connector 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B7A03CE-DE21-ED51-01B8-A544AA21136D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="9196524" y="20249045"/>
+          <a:ext cx="7219757" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>91440</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>128803</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>5443</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>128803</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="Straight Arrow Connector 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FE3085F-79C2-EB32-BB02-EA908C7E96D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14721840" y="18607303"/>
+          <a:ext cx="1742803" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>107769</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>528774</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>110054</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Rectangle 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F970C2B-B062-4B21-B471-34220D71E650}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17786169" y="12439649"/>
+          <a:ext cx="1030605" cy="433905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>send help (if no answer after 10sec)</a:t>
+            <a:t>Browser</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1000">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Fall Dashboard</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1000">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>56879</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>489314</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>110055</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Rectangle 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09BFC6B5-F071-D2AD-38A5-F7C911FBBC34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15906479" y="12439650"/>
+          <a:ext cx="1042035" cy="433905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>background</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Task (writer + trigerer)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="900">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>171577</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>88351</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>416186</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>150523</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="Rectangle 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7ADA631C-9E5D-4977-853B-FC6E7AA570FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9315577" y="19940692"/>
+          <a:ext cx="6950209" cy="254913"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Writes fall_history table</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-GB">
               <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Obsrv_id, pat_id, dev_id, pat_confirmed</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>needs_help, detected_time,  alert_time</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
               </a:solidFill>
             </a:rPr>
             <a:t> </a:t>
           </a:r>
           <a:endParaRPr lang="en-DE" sz="1050" b="0">
             <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="85000"/>
+                <a:lumOff val="15000"/>
+              </a:schemeClr>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -18656,7 +19671,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AEB2071-28A2-48BB-B77C-31D6CC6F6BEA}">
-  <dimension ref="B2:AG110"/>
+  <dimension ref="B2:AG111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="8"/>
@@ -20436,7 +21451,7 @@
       <c r="Z68" s="13"/>
       <c r="AA68" s="20"/>
       <c r="AB68" s="13"/>
-      <c r="AC68" s="9"/>
+      <c r="AC68" s="13"/>
       <c r="AD68" s="20"/>
       <c r="AE68" s="13"/>
       <c r="AF68" s="9"/>
@@ -20470,7 +21485,7 @@
       <c r="Z69" s="13"/>
       <c r="AA69" s="20"/>
       <c r="AB69" s="13"/>
-      <c r="AC69" s="9"/>
+      <c r="AC69" s="13"/>
       <c r="AD69" s="20"/>
       <c r="AE69" s="13"/>
       <c r="AF69" s="9"/>
@@ -20504,7 +21519,7 @@
       <c r="Z70" s="13"/>
       <c r="AA70" s="20"/>
       <c r="AB70" s="13"/>
-      <c r="AC70" s="9"/>
+      <c r="AC70" s="13"/>
       <c r="AD70" s="20"/>
       <c r="AE70" s="13"/>
       <c r="AF70" s="9"/>
@@ -20538,7 +21553,7 @@
       <c r="Z71" s="13"/>
       <c r="AA71" s="20"/>
       <c r="AB71" s="13"/>
-      <c r="AC71" s="9"/>
+      <c r="AC71" s="13"/>
       <c r="AD71" s="20"/>
       <c r="AE71" s="13"/>
       <c r="AF71" s="9"/>
@@ -20572,7 +21587,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="20"/>
       <c r="AB72" s="13"/>
-      <c r="AC72" s="9"/>
+      <c r="AC72" s="13"/>
       <c r="AD72" s="20"/>
       <c r="AE72" s="13"/>
       <c r="AF72" s="9"/>
@@ -20606,7 +21621,7 @@
       <c r="Z73" s="13"/>
       <c r="AA73" s="20"/>
       <c r="AB73" s="13"/>
-      <c r="AC73" s="9"/>
+      <c r="AC73" s="13"/>
       <c r="AD73" s="20"/>
       <c r="AE73" s="13"/>
       <c r="AF73" s="9"/>
@@ -20640,7 +21655,7 @@
       <c r="Z74" s="13"/>
       <c r="AA74" s="20"/>
       <c r="AB74" s="13"/>
-      <c r="AC74" s="9"/>
+      <c r="AC74" s="13"/>
       <c r="AD74" s="20"/>
       <c r="AE74" s="13"/>
       <c r="AF74" s="9"/>
@@ -20674,7 +21689,7 @@
       <c r="Z75" s="13"/>
       <c r="AA75" s="20"/>
       <c r="AB75" s="13"/>
-      <c r="AC75" s="9"/>
+      <c r="AC75" s="13"/>
       <c r="AD75" s="20"/>
       <c r="AE75" s="13"/>
       <c r="AF75" s="9"/>
@@ -20708,7 +21723,7 @@
       <c r="Z76" s="13"/>
       <c r="AA76" s="20"/>
       <c r="AB76" s="13"/>
-      <c r="AC76" s="9"/>
+      <c r="AC76" s="13"/>
       <c r="AD76" s="20"/>
       <c r="AE76" s="13"/>
       <c r="AF76" s="9"/>
@@ -20742,7 +21757,7 @@
       <c r="Z77" s="13"/>
       <c r="AA77" s="20"/>
       <c r="AB77" s="13"/>
-      <c r="AC77" s="9"/>
+      <c r="AC77" s="13"/>
       <c r="AD77" s="20"/>
       <c r="AE77" s="13"/>
       <c r="AF77" s="9"/>
@@ -20776,7 +21791,7 @@
       <c r="Z78" s="13"/>
       <c r="AA78" s="20"/>
       <c r="AB78" s="13"/>
-      <c r="AC78" s="9"/>
+      <c r="AC78" s="13"/>
       <c r="AD78" s="20"/>
       <c r="AE78" s="13"/>
       <c r="AF78" s="9"/>
@@ -20810,7 +21825,7 @@
       <c r="Z79" s="13"/>
       <c r="AA79" s="20"/>
       <c r="AB79" s="13"/>
-      <c r="AC79" s="9"/>
+      <c r="AC79" s="13"/>
       <c r="AD79" s="20"/>
       <c r="AE79" s="13"/>
       <c r="AF79" s="9"/>
@@ -20844,7 +21859,7 @@
       <c r="Z80" s="13"/>
       <c r="AA80" s="20"/>
       <c r="AB80" s="13"/>
-      <c r="AC80" s="9"/>
+      <c r="AC80" s="13"/>
       <c r="AD80" s="20"/>
       <c r="AE80" s="13"/>
       <c r="AF80" s="9"/>
@@ -20880,7 +21895,7 @@
       <c r="Z81" s="13"/>
       <c r="AA81" s="20"/>
       <c r="AB81" s="13"/>
-      <c r="AC81" s="9"/>
+      <c r="AC81" s="13"/>
       <c r="AD81" s="20"/>
       <c r="AE81" s="13"/>
       <c r="AF81" s="9"/>
@@ -20916,7 +21931,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="20"/>
       <c r="AB82" s="13"/>
-      <c r="AC82" s="9"/>
+      <c r="AC82" s="13"/>
       <c r="AD82" s="20"/>
       <c r="AE82" s="13"/>
       <c r="AF82" s="9"/>
@@ -20935,7 +21950,9 @@
       <c r="K83" s="13"/>
       <c r="L83" s="20"/>
       <c r="M83" s="13"/>
-      <c r="N83" s="9"/>
+      <c r="N83" s="30" t="s">
+        <v>105</v>
+      </c>
       <c r="O83" s="9"/>
       <c r="P83" s="21"/>
       <c r="Q83" s="12"/>
@@ -20950,7 +21967,7 @@
       <c r="Z83" s="13"/>
       <c r="AA83" s="20"/>
       <c r="AB83" s="13"/>
-      <c r="AC83" s="9"/>
+      <c r="AC83" s="13"/>
       <c r="AD83" s="20"/>
       <c r="AE83" s="13"/>
       <c r="AF83" s="9"/>
@@ -20969,8 +21986,8 @@
       <c r="K84" s="13"/>
       <c r="L84" s="20"/>
       <c r="M84" s="13"/>
-      <c r="N84" s="9" t="s">
-        <v>105</v>
+      <c r="N84" s="11" t="s">
+        <v>106</v>
       </c>
       <c r="O84" s="9"/>
       <c r="P84" s="21"/>
@@ -20986,7 +22003,7 @@
       <c r="Z84" s="13"/>
       <c r="AA84" s="20"/>
       <c r="AB84" s="13"/>
-      <c r="AC84" s="9"/>
+      <c r="AC84" s="13"/>
       <c r="AD84" s="20"/>
       <c r="AE84" s="13"/>
       <c r="AF84" s="9"/>
@@ -21006,7 +22023,7 @@
       <c r="L85" s="20"/>
       <c r="M85" s="13"/>
       <c r="N85" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O85" s="9"/>
       <c r="P85" s="21"/>
@@ -21022,7 +22039,7 @@
       <c r="Z85" s="13"/>
       <c r="AA85" s="20"/>
       <c r="AB85" s="13"/>
-      <c r="AC85" s="9"/>
+      <c r="AC85" s="13"/>
       <c r="AD85" s="20"/>
       <c r="AE85" s="13"/>
       <c r="AF85" s="9"/>
@@ -21056,7 +22073,7 @@
       <c r="Z86" s="13"/>
       <c r="AA86" s="20"/>
       <c r="AB86" s="13"/>
-      <c r="AC86" s="9"/>
+      <c r="AC86" s="13"/>
       <c r="AD86" s="20"/>
       <c r="AE86" s="13"/>
       <c r="AF86" s="9"/>
@@ -21090,9 +22107,7 @@
       <c r="Z87" s="13"/>
       <c r="AA87" s="20"/>
       <c r="AB87" s="13"/>
-      <c r="AC87" s="9" t="s">
-        <v>107</v>
-      </c>
+      <c r="AC87" s="13"/>
       <c r="AD87" s="20"/>
       <c r="AE87" s="13"/>
       <c r="AF87" s="9"/>
@@ -21126,7 +22141,7 @@
       <c r="Z88" s="13"/>
       <c r="AA88" s="20"/>
       <c r="AB88" s="13"/>
-      <c r="AC88" s="9"/>
+      <c r="AC88" s="13"/>
       <c r="AD88" s="20"/>
       <c r="AE88" s="13"/>
       <c r="AF88" s="9"/>
@@ -21160,7 +22175,7 @@
       <c r="Z89" s="13"/>
       <c r="AA89" s="20"/>
       <c r="AB89" s="13"/>
-      <c r="AC89" s="9"/>
+      <c r="AC89" s="13"/>
       <c r="AD89" s="20"/>
       <c r="AE89" s="13"/>
       <c r="AF89" s="9"/>
@@ -21194,7 +22209,7 @@
       <c r="Z90" s="13"/>
       <c r="AA90" s="20"/>
       <c r="AB90" s="13"/>
-      <c r="AC90" s="9"/>
+      <c r="AC90" s="13"/>
       <c r="AD90" s="20"/>
       <c r="AE90" s="13"/>
       <c r="AF90" s="9"/>
@@ -21228,7 +22243,7 @@
       <c r="Z91" s="13"/>
       <c r="AA91" s="20"/>
       <c r="AB91" s="13"/>
-      <c r="AC91" s="9"/>
+      <c r="AC91" s="13"/>
       <c r="AD91" s="20"/>
       <c r="AE91" s="13"/>
       <c r="AF91" s="9"/>
@@ -21244,7 +22259,7 @@
       <c r="H92" s="13"/>
       <c r="I92" s="9"/>
       <c r="J92" s="21"/>
-      <c r="K92" s="13"/>
+      <c r="K92" s="17"/>
       <c r="L92" s="20"/>
       <c r="M92" s="13"/>
       <c r="N92" s="12"/>
@@ -21253,16 +22268,16 @@
       <c r="Q92" s="12"/>
       <c r="R92" s="9"/>
       <c r="S92" s="21"/>
-      <c r="T92" s="13"/>
+      <c r="T92" s="17"/>
       <c r="U92" s="20"/>
       <c r="V92" s="13"/>
-      <c r="W92" s="13"/>
+      <c r="W92" s="12"/>
       <c r="X92" s="9"/>
       <c r="Y92" s="21"/>
       <c r="Z92" s="13"/>
       <c r="AA92" s="20"/>
       <c r="AB92" s="13"/>
-      <c r="AC92" s="9"/>
+      <c r="AC92" s="13"/>
       <c r="AD92" s="20"/>
       <c r="AE92" s="13"/>
       <c r="AF92" s="9"/>
@@ -21278,7 +22293,7 @@
       <c r="H93" s="13"/>
       <c r="I93" s="9"/>
       <c r="J93" s="21"/>
-      <c r="K93" s="13"/>
+      <c r="K93" s="17"/>
       <c r="L93" s="20"/>
       <c r="M93" s="13"/>
       <c r="N93" s="12"/>
@@ -21287,16 +22302,16 @@
       <c r="Q93" s="12"/>
       <c r="R93" s="9"/>
       <c r="S93" s="21"/>
-      <c r="T93" s="13"/>
+      <c r="T93" s="17"/>
       <c r="U93" s="20"/>
       <c r="V93" s="13"/>
-      <c r="W93" s="13"/>
+      <c r="W93" s="12"/>
       <c r="X93" s="9"/>
       <c r="Y93" s="21"/>
       <c r="Z93" s="13"/>
       <c r="AA93" s="20"/>
       <c r="AB93" s="13"/>
-      <c r="AC93" s="9"/>
+      <c r="AC93" s="13"/>
       <c r="AD93" s="20"/>
       <c r="AE93" s="13"/>
       <c r="AF93" s="9"/>
@@ -21312,7 +22327,7 @@
       <c r="H94" s="13"/>
       <c r="I94" s="9"/>
       <c r="J94" s="21"/>
-      <c r="K94" s="13"/>
+      <c r="K94" s="17"/>
       <c r="L94" s="20"/>
       <c r="M94" s="13"/>
       <c r="N94" s="12"/>
@@ -21321,16 +22336,18 @@
       <c r="Q94" s="12"/>
       <c r="R94" s="9"/>
       <c r="S94" s="21"/>
-      <c r="T94" s="13"/>
+      <c r="T94" s="17" t="s">
+        <v>72</v>
+      </c>
       <c r="U94" s="20"/>
       <c r="V94" s="13"/>
-      <c r="W94" s="13"/>
+      <c r="W94" s="12"/>
       <c r="X94" s="9"/>
       <c r="Y94" s="21"/>
       <c r="Z94" s="13"/>
       <c r="AA94" s="20"/>
       <c r="AB94" s="13"/>
-      <c r="AC94" s="9"/>
+      <c r="AC94" s="13"/>
       <c r="AD94" s="20"/>
       <c r="AE94" s="13"/>
       <c r="AF94" s="9"/>
@@ -21355,16 +22372,18 @@
       <c r="Q95" s="12"/>
       <c r="R95" s="9"/>
       <c r="S95" s="21"/>
-      <c r="T95" s="13"/>
+      <c r="T95" s="17"/>
       <c r="U95" s="20"/>
       <c r="V95" s="13"/>
-      <c r="W95" s="13"/>
+      <c r="W95" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="X95" s="9"/>
       <c r="Y95" s="21"/>
-      <c r="Z95" s="13"/>
+      <c r="Z95" s="19"/>
       <c r="AA95" s="20"/>
       <c r="AB95" s="13"/>
-      <c r="AC95" s="9"/>
+      <c r="AC95" s="19"/>
       <c r="AD95" s="20"/>
       <c r="AE95" s="13"/>
       <c r="AF95" s="9"/>
@@ -21392,13 +22411,15 @@
       <c r="T96" s="17"/>
       <c r="U96" s="20"/>
       <c r="V96" s="13"/>
-      <c r="W96" s="12"/>
+      <c r="W96" s="12" t="s">
+        <v>73</v>
+      </c>
       <c r="X96" s="9"/>
       <c r="Y96" s="21"/>
-      <c r="Z96" s="13"/>
+      <c r="Z96" s="19"/>
       <c r="AA96" s="20"/>
       <c r="AB96" s="13"/>
-      <c r="AC96" s="9"/>
+      <c r="AC96" s="19"/>
       <c r="AD96" s="20"/>
       <c r="AE96" s="13"/>
       <c r="AF96" s="9"/>
@@ -21414,7 +22435,7 @@
       <c r="H97" s="13"/>
       <c r="I97" s="9"/>
       <c r="J97" s="21"/>
-      <c r="K97" s="18"/>
+      <c r="K97" s="13"/>
       <c r="L97" s="20"/>
       <c r="M97" s="13"/>
       <c r="N97" s="12"/>
@@ -21426,13 +22447,13 @@
       <c r="T97" s="17"/>
       <c r="U97" s="20"/>
       <c r="V97" s="13"/>
-      <c r="W97" s="12"/>
+      <c r="W97" s="13"/>
       <c r="X97" s="9"/>
       <c r="Y97" s="21"/>
       <c r="Z97" s="13"/>
       <c r="AA97" s="20"/>
       <c r="AB97" s="13"/>
-      <c r="AC97" s="9"/>
+      <c r="AC97" s="13"/>
       <c r="AD97" s="20"/>
       <c r="AE97" s="13"/>
       <c r="AF97" s="9"/>
@@ -21448,7 +22469,7 @@
       <c r="H98" s="13"/>
       <c r="I98" s="9"/>
       <c r="J98" s="21"/>
-      <c r="K98" s="17"/>
+      <c r="K98" s="13"/>
       <c r="L98" s="20"/>
       <c r="M98" s="13"/>
       <c r="N98" s="12"/>
@@ -21460,13 +22481,13 @@
       <c r="T98" s="17"/>
       <c r="U98" s="20"/>
       <c r="V98" s="13"/>
-      <c r="W98" s="12"/>
+      <c r="W98" s="13"/>
       <c r="X98" s="9"/>
       <c r="Y98" s="21"/>
       <c r="Z98" s="13"/>
       <c r="AA98" s="20"/>
       <c r="AB98" s="13"/>
-      <c r="AC98" s="9"/>
+      <c r="AC98" s="13"/>
       <c r="AD98" s="20"/>
       <c r="AE98" s="13"/>
       <c r="AF98" s="9"/>
@@ -21482,27 +22503,27 @@
       <c r="H99" s="13"/>
       <c r="I99" s="9"/>
       <c r="J99" s="21"/>
-      <c r="K99" s="17"/>
+      <c r="K99" s="13"/>
       <c r="L99" s="20"/>
       <c r="M99" s="13"/>
-      <c r="N99" s="12"/>
+      <c r="N99" s="9"/>
       <c r="O99" s="9"/>
       <c r="P99" s="21"/>
-      <c r="Q99" s="12"/>
+      <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
       <c r="S99" s="21"/>
-      <c r="T99" s="17"/>
+      <c r="T99" s="22"/>
       <c r="U99" s="20"/>
       <c r="V99" s="13"/>
-      <c r="W99" s="12" t="s">
-        <v>74</v>
-      </c>
+      <c r="W99" s="13"/>
       <c r="X99" s="9"/>
       <c r="Y99" s="21"/>
       <c r="Z99" s="13"/>
       <c r="AA99" s="20"/>
       <c r="AB99" s="13"/>
-      <c r="AC99" s="9"/>
+      <c r="AC99" s="14" t="s">
+        <v>108</v>
+      </c>
       <c r="AD99" s="20"/>
       <c r="AE99" s="13"/>
       <c r="AF99" s="9"/>
@@ -21518,29 +22539,25 @@
       <c r="H100" s="13"/>
       <c r="I100" s="9"/>
       <c r="J100" s="21"/>
-      <c r="K100" s="17"/>
+      <c r="K100" s="13"/>
       <c r="L100" s="20"/>
       <c r="M100" s="13"/>
-      <c r="N100" s="12"/>
+      <c r="N100" s="9"/>
       <c r="O100" s="9"/>
       <c r="P100" s="21"/>
-      <c r="Q100" s="12"/>
+      <c r="Q100" s="9"/>
       <c r="R100" s="9"/>
       <c r="S100" s="21"/>
-      <c r="T100" s="17" t="s">
-        <v>72</v>
-      </c>
+      <c r="T100" s="22"/>
       <c r="U100" s="20"/>
       <c r="V100" s="13"/>
-      <c r="W100" s="12" t="s">
-        <v>73</v>
-      </c>
+      <c r="W100" s="13"/>
       <c r="X100" s="9"/>
       <c r="Y100" s="21"/>
       <c r="Z100" s="13"/>
       <c r="AA100" s="20"/>
       <c r="AB100" s="13"/>
-      <c r="AC100" s="9"/>
+      <c r="AC100" s="13"/>
       <c r="AD100" s="20"/>
       <c r="AE100" s="13"/>
       <c r="AF100" s="9"/>
@@ -21559,13 +22576,13 @@
       <c r="K101" s="13"/>
       <c r="L101" s="20"/>
       <c r="M101" s="13"/>
-      <c r="N101" s="12"/>
+      <c r="N101" s="9"/>
       <c r="O101" s="9"/>
       <c r="P101" s="21"/>
-      <c r="Q101" s="12"/>
+      <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
       <c r="S101" s="21"/>
-      <c r="T101" s="17"/>
+      <c r="T101" s="22"/>
       <c r="U101" s="20"/>
       <c r="V101" s="13"/>
       <c r="W101" s="13"/>
@@ -21574,7 +22591,7 @@
       <c r="Z101" s="13"/>
       <c r="AA101" s="20"/>
       <c r="AB101" s="13"/>
-      <c r="AC101" s="9"/>
+      <c r="AC101" s="13"/>
       <c r="AD101" s="20"/>
       <c r="AE101" s="13"/>
       <c r="AF101" s="9"/>
@@ -21593,13 +22610,13 @@
       <c r="K102" s="13"/>
       <c r="L102" s="20"/>
       <c r="M102" s="13"/>
-      <c r="N102" s="12"/>
+      <c r="N102" s="9"/>
       <c r="O102" s="9"/>
       <c r="P102" s="21"/>
-      <c r="Q102" s="12"/>
+      <c r="Q102" s="9"/>
       <c r="R102" s="9"/>
       <c r="S102" s="21"/>
-      <c r="T102" s="17"/>
+      <c r="T102" s="22"/>
       <c r="U102" s="20"/>
       <c r="V102" s="13"/>
       <c r="W102" s="13"/>
@@ -21608,7 +22625,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="20"/>
       <c r="AB102" s="13"/>
-      <c r="AC102" s="9"/>
+      <c r="AC102" s="13"/>
       <c r="AD102" s="20"/>
       <c r="AE102" s="13"/>
       <c r="AF102" s="9"/>
@@ -21627,24 +22644,22 @@
       <c r="K103" s="13"/>
       <c r="L103" s="20"/>
       <c r="M103" s="13"/>
-      <c r="N103" s="12"/>
+      <c r="N103" s="30"/>
       <c r="O103" s="9"/>
       <c r="P103" s="21"/>
-      <c r="Q103" s="12"/>
+      <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
       <c r="S103" s="21"/>
-      <c r="T103" s="17"/>
+      <c r="T103" s="22"/>
       <c r="U103" s="20"/>
       <c r="V103" s="13"/>
       <c r="W103" s="13"/>
       <c r="X103" s="9"/>
       <c r="Y103" s="21"/>
-      <c r="Z103" s="19" t="s">
-        <v>59</v>
-      </c>
+      <c r="Z103" s="13"/>
       <c r="AA103" s="20"/>
       <c r="AB103" s="13"/>
-      <c r="AC103" s="9"/>
+      <c r="AC103" s="13"/>
       <c r="AD103" s="20"/>
       <c r="AE103" s="13"/>
       <c r="AF103" s="9"/>
@@ -21663,24 +22678,22 @@
       <c r="K104" s="13"/>
       <c r="L104" s="20"/>
       <c r="M104" s="13"/>
-      <c r="N104" s="12"/>
+      <c r="N104" s="11"/>
       <c r="O104" s="9"/>
       <c r="P104" s="21"/>
-      <c r="Q104" s="12"/>
+      <c r="Q104" s="9"/>
       <c r="R104" s="9"/>
       <c r="S104" s="21"/>
-      <c r="T104" s="17"/>
+      <c r="T104" s="22"/>
       <c r="U104" s="20"/>
       <c r="V104" s="13"/>
       <c r="W104" s="13"/>
       <c r="X104" s="9"/>
       <c r="Y104" s="21"/>
-      <c r="Z104" s="19" t="s">
-        <v>60</v>
-      </c>
+      <c r="Z104" s="13"/>
       <c r="AA104" s="20"/>
       <c r="AB104" s="13"/>
-      <c r="AC104" s="9"/>
+      <c r="AC104" s="13"/>
       <c r="AD104" s="20"/>
       <c r="AE104" s="13"/>
       <c r="AF104" s="9"/>
@@ -21699,7 +22712,7 @@
       <c r="K105" s="13"/>
       <c r="L105" s="20"/>
       <c r="M105" s="13"/>
-      <c r="N105" s="9"/>
+      <c r="N105" s="11"/>
       <c r="O105" s="9"/>
       <c r="P105" s="21"/>
       <c r="Q105" s="9"/>
@@ -21714,7 +22727,7 @@
       <c r="Z105" s="13"/>
       <c r="AA105" s="20"/>
       <c r="AB105" s="13"/>
-      <c r="AC105" s="9"/>
+      <c r="AC105" s="13"/>
       <c r="AD105" s="20"/>
       <c r="AE105" s="13"/>
       <c r="AF105" s="9"/>
@@ -21748,7 +22761,7 @@
       <c r="Z106" s="13"/>
       <c r="AA106" s="20"/>
       <c r="AB106" s="13"/>
-      <c r="AC106" s="9"/>
+      <c r="AC106" s="13"/>
       <c r="AD106" s="20"/>
       <c r="AE106" s="13"/>
       <c r="AF106" s="9"/>
@@ -21782,7 +22795,7 @@
       <c r="Z107" s="13"/>
       <c r="AA107" s="20"/>
       <c r="AB107" s="13"/>
-      <c r="AC107" s="9"/>
+      <c r="AC107" s="13"/>
       <c r="AD107" s="20"/>
       <c r="AE107" s="13"/>
       <c r="AF107" s="9"/>
@@ -21816,7 +22829,7 @@
       <c r="Z108" s="13"/>
       <c r="AA108" s="20"/>
       <c r="AB108" s="13"/>
-      <c r="AC108" s="9"/>
+      <c r="AC108" s="13"/>
       <c r="AD108" s="20"/>
       <c r="AE108" s="13"/>
       <c r="AF108" s="9"/>
@@ -21825,34 +22838,34 @@
     <row r="109" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
-      <c r="D109" s="9"/>
-      <c r="E109" s="9"/>
-      <c r="F109" s="9"/>
-      <c r="G109" s="9"/>
-      <c r="H109" s="9"/>
+      <c r="D109" s="21"/>
+      <c r="E109" s="13"/>
+      <c r="F109" s="20"/>
+      <c r="G109" s="13"/>
+      <c r="H109" s="13"/>
       <c r="I109" s="9"/>
-      <c r="J109" s="9"/>
-      <c r="K109" s="9"/>
-      <c r="L109" s="9"/>
-      <c r="M109" s="9"/>
+      <c r="J109" s="21"/>
+      <c r="K109" s="13"/>
+      <c r="L109" s="20"/>
+      <c r="M109" s="13"/>
       <c r="N109" s="9"/>
       <c r="O109" s="9"/>
-      <c r="P109" s="9"/>
+      <c r="P109" s="21"/>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
-      <c r="S109" s="9"/>
-      <c r="T109" s="9"/>
-      <c r="U109" s="9"/>
-      <c r="V109" s="9"/>
-      <c r="W109" s="9"/>
+      <c r="S109" s="21"/>
+      <c r="T109" s="22"/>
+      <c r="U109" s="20"/>
+      <c r="V109" s="13"/>
+      <c r="W109" s="13"/>
       <c r="X109" s="9"/>
-      <c r="Y109" s="9"/>
-      <c r="Z109" s="9"/>
-      <c r="AA109" s="9"/>
-      <c r="AB109" s="9"/>
-      <c r="AC109" s="9"/>
-      <c r="AD109" s="9"/>
-      <c r="AE109" s="9"/>
+      <c r="Y109" s="21"/>
+      <c r="Z109" s="13"/>
+      <c r="AA109" s="20"/>
+      <c r="AB109" s="13"/>
+      <c r="AC109" s="13"/>
+      <c r="AD109" s="20"/>
+      <c r="AE109" s="13"/>
       <c r="AF109" s="9"/>
       <c r="AG109" s="9"/>
     </row>
@@ -21889,6 +22902,40 @@
       <c r="AE110" s="9"/>
       <c r="AF110" s="9"/>
       <c r="AG110" s="9"/>
+    </row>
+    <row r="111" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
+      <c r="D111" s="9"/>
+      <c r="E111" s="9"/>
+      <c r="F111" s="9"/>
+      <c r="G111" s="9"/>
+      <c r="H111" s="9"/>
+      <c r="I111" s="9"/>
+      <c r="J111" s="9"/>
+      <c r="K111" s="9"/>
+      <c r="L111" s="9"/>
+      <c r="M111" s="9"/>
+      <c r="N111" s="9"/>
+      <c r="O111" s="9"/>
+      <c r="P111" s="9"/>
+      <c r="Q111" s="9"/>
+      <c r="R111" s="9"/>
+      <c r="S111" s="9"/>
+      <c r="T111" s="9"/>
+      <c r="U111" s="9"/>
+      <c r="V111" s="9"/>
+      <c r="W111" s="9"/>
+      <c r="X111" s="9"/>
+      <c r="Y111" s="9"/>
+      <c r="Z111" s="9"/>
+      <c r="AA111" s="9"/>
+      <c r="AB111" s="9"/>
+      <c r="AC111" s="9"/>
+      <c r="AD111" s="9"/>
+      <c r="AE111" s="9"/>
+      <c r="AF111" s="9"/>
+      <c r="AG111" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_concept_6G_integration/MCS_Fall_Detection.xlsx
+++ b/_concept_6G_integration/MCS_Fall_Detection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hayat\Documents\6G\FallDetection_new\_concept_6G_integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE1DE29-E6B3-469E-8F3F-5AE37890C4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA650CF-BBE3-4C6E-9889-3B62ACDAAACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="-2970" windowWidth="23232" windowHeight="13872" activeTab="2" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
+    <workbookView xWindow="20544" yWindow="-2970" windowWidth="23232" windowHeight="13872" activeTab="3" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4894,14 +4894,14 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>436583</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>167096</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>5442</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>168330</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>108857</xdr:rowOff>
+      <xdr:rowOff>110761</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4916,8 +4916,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10190183" y="4662896"/>
-          <a:ext cx="1560547" cy="1465761"/>
+          <a:off x="10190183" y="4882242"/>
+          <a:ext cx="1560547" cy="1248319"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6464,14 +6464,14 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>20732</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>76199</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>445658</xdr:colOff>
+      <xdr:colOff>447563</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>28798</xdr:rowOff>
+      <xdr:rowOff>30703</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6486,8 +6486,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5507132" y="4762499"/>
-          <a:ext cx="1644126" cy="3191099"/>
+          <a:off x="5507132" y="4648200"/>
+          <a:ext cx="1646031" cy="3307303"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6625,15 +6625,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>260488</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>183105</xdr:rowOff>
+      <xdr:colOff>269742</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>50843</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>276561</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>144124</xdr:rowOff>
+      <xdr:colOff>285815</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>11862</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6648,8 +6648,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5746888" y="5100246"/>
-          <a:ext cx="1235273" cy="731984"/>
+          <a:off x="5756142" y="5499143"/>
+          <a:ext cx="1235273" cy="723019"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6726,16 +6726,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>104183</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>189810</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>340131</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>70067</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>523283</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>75511</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>149631</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>146268</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6750,7 +6750,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10467383" y="5447610"/>
+          <a:off x="5826531" y="4756367"/>
           <a:ext cx="1028700" cy="647701"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6826,15 +6826,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>131285</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>26142</xdr:rowOff>
+      <xdr:colOff>98628</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>55262</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>550385</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>104583</xdr:rowOff>
+      <xdr:colOff>517728</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>133703</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6849,7 +6849,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10494485" y="4712442"/>
+          <a:off x="10461828" y="5122562"/>
           <a:ext cx="1028700" cy="649941"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6925,15 +6925,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>350086</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>125384</xdr:rowOff>
+      <xdr:colOff>166934</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>67418</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>145226</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>571674</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>5715</xdr:rowOff>
+      <xdr:rowOff>138249</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6948,8 +6948,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5836486" y="6969937"/>
-          <a:ext cx="1014340" cy="844037"/>
+          <a:off x="5653334" y="7039718"/>
+          <a:ext cx="1014340" cy="832831"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7456,15 +7456,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>227156</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>20944</xdr:rowOff>
+      <xdr:colOff>270700</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>91701</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>260536</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>78722</xdr:rowOff>
+      <xdr:colOff>307890</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>149479</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7479,8 +7479,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5713556" y="6094532"/>
-          <a:ext cx="1252580" cy="636002"/>
+          <a:off x="5757100" y="6302001"/>
+          <a:ext cx="1256390" cy="629278"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7973,13 +7973,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>499141</xdr:colOff>
-      <xdr:row>114</xdr:row>
+      <xdr:row>115</xdr:row>
       <xdr:rowOff>66482</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>321704</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>46196</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -11213,7 +11213,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Task (writer)</a:t>
+            <a:t>Task </a:t>
           </a:r>
           <a:endParaRPr lang="en-DE" sz="900">
             <a:effectLst/>
@@ -11391,7 +11391,7 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>142874</xdr:colOff>
+      <xdr:colOff>144779</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
@@ -11414,7 +11414,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="754379" y="304800"/>
+          <a:off x="754379" y="11544300"/>
           <a:ext cx="6694171" cy="327660"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -11451,15 +11451,7 @@
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>Fall History Dashboard (needs</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="2000" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> update)</a:t>
+            <a:t>Fall History Dashboard </a:t>
           </a:r>
           <a:endParaRPr lang="en-DE" sz="2000" b="1">
             <a:solidFill>
@@ -11767,13 +11759,13 @@
     <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>56606</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>117437</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>569868</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>117437</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -11831,14 +11823,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>38373</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:colOff>327212</xdr:colOff>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>150189</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>555812</xdr:colOff>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>150189</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -11854,8 +11846,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="16497573" y="19200189"/>
-          <a:ext cx="1790427" cy="0"/>
+          <a:off x="16786412" y="19424307"/>
+          <a:ext cx="1447800" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -12056,11 +12048,37 @@
           <a:r>
             <a:rPr lang="en-GB" sz="900" b="0">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Backend</a:t>
-          </a:r>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Backend </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Compnents / System</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="900" b="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="85000"/>
+                <a:lumOff val="15000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -12240,7 +12258,7 @@
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t> App</a:t>
+            <a:t> App Compnents / System</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="900" b="0">
             <a:solidFill>
@@ -12321,13 +12339,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>49529</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>96066</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>511629</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>96066</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -12462,15 +12480,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>60688</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>63489</xdr:rowOff>
+      <xdr:colOff>49147</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>90942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>1905</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>120540</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>599964</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>147993</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -12485,8 +12503,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13471888" y="19113489"/>
-          <a:ext cx="550817" cy="438051"/>
+          <a:off x="13460347" y="18594095"/>
+          <a:ext cx="550817" cy="442533"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12641,13 +12659,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>161652</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>134981</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>560614</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>134981</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -12706,13 +12724,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>67764</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>119342</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>575311</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>119342</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -12771,13 +12789,13 @@
     <xdr:from>
       <xdr:col>18</xdr:col>
       <xdr:colOff>189140</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>87902</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>512718</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>87902</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -13099,15 +13117,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>164519</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>167639</xdr:rowOff>
+      <xdr:colOff>166424</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>130629</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>555812</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>70965</xdr:rowOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>72870</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -13122,8 +13140,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1993319" y="17321604"/>
-          <a:ext cx="8925693" cy="288808"/>
+          <a:off x="1995224" y="16704129"/>
+          <a:ext cx="8923788" cy="323241"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -13333,13 +13351,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>51236</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>31024</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>566057</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>14548</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -13552,13 +13570,13 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>450124</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>20138</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>117455</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>140278</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -13725,15 +13743,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>118655</xdr:colOff>
+      <xdr:colOff>151312</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>86268</xdr:rowOff>
+      <xdr:rowOff>160835</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>442233</xdr:colOff>
+      <xdr:colOff>474890</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>86268</xdr:rowOff>
+      <xdr:rowOff>160835</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -13748,7 +13766,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7433855" y="16278768"/>
+          <a:off x="7466512" y="16353335"/>
           <a:ext cx="1542778" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -13791,13 +13809,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>107225</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>111306</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>582386</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>85453</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -13921,13 +13939,13 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>52524</xdr:colOff>
-      <xdr:row>105</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>11221</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>566681</xdr:colOff>
-      <xdr:row>105</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>11221</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -13986,13 +14004,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>91440</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>128803</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>5443</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>128803</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -14221,7 +14239,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Task (writer + trigerer)</a:t>
+            <a:t>Task </a:t>
           </a:r>
           <a:endParaRPr lang="en-DE" sz="900">
             <a:effectLst/>
@@ -14235,13 +14253,13 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>171577</xdr:colOff>
-      <xdr:row>103</xdr:row>
+      <xdr:row>104</xdr:row>
       <xdr:rowOff>88351</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>416186</xdr:colOff>
-      <xdr:row>104</xdr:row>
+      <xdr:row>105</xdr:row>
       <xdr:rowOff>150523</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -14378,6 +14396,219 @@
                 <a:lumOff val="15000"/>
               </a:schemeClr>
             </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>306546</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>8964</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>247763</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>181273</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="Rectangle 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4583E2E-FFF3-28B5-39CE-1FD6E06A9061}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16156146" y="20054046"/>
+          <a:ext cx="550817" cy="365051"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>writer</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>306546</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>163269</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>247763</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>142837</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="Rectangle 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BD66321-4727-684F-B34C-00FDDFE25BA1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16156146" y="19244645"/>
+          <a:ext cx="550817" cy="365051"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>streamer</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1000">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>357436</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>3794</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>300558</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>173862</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Rectangle 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62AA6709-2187-4623-4F90-DD62F8F78338}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7063036" y="16196294"/>
+          <a:ext cx="552722" cy="360568"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>writer</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:effectLst/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -19671,7 +19902,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AEB2071-28A2-48BB-B77C-31D6CC6F6BEA}">
-  <dimension ref="B2:AG111"/>
+  <dimension ref="B2:AG112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="8"/>
@@ -22126,7 +22357,7 @@
       <c r="K88" s="13"/>
       <c r="L88" s="20"/>
       <c r="M88" s="13"/>
-      <c r="N88" s="17"/>
+      <c r="N88" s="9"/>
       <c r="O88" s="9"/>
       <c r="P88" s="21"/>
       <c r="Q88" s="12"/>
@@ -22160,7 +22391,7 @@
       <c r="K89" s="13"/>
       <c r="L89" s="20"/>
       <c r="M89" s="13"/>
-      <c r="N89" s="12"/>
+      <c r="N89" s="17"/>
       <c r="O89" s="9"/>
       <c r="P89" s="21"/>
       <c r="Q89" s="12"/>
@@ -22259,7 +22490,7 @@
       <c r="H92" s="13"/>
       <c r="I92" s="9"/>
       <c r="J92" s="21"/>
-      <c r="K92" s="17"/>
+      <c r="K92" s="13"/>
       <c r="L92" s="20"/>
       <c r="M92" s="13"/>
       <c r="N92" s="12"/>
@@ -22268,10 +22499,10 @@
       <c r="Q92" s="12"/>
       <c r="R92" s="9"/>
       <c r="S92" s="21"/>
-      <c r="T92" s="17"/>
+      <c r="T92" s="13"/>
       <c r="U92" s="20"/>
       <c r="V92" s="13"/>
-      <c r="W92" s="12"/>
+      <c r="W92" s="13"/>
       <c r="X92" s="9"/>
       <c r="Y92" s="21"/>
       <c r="Z92" s="13"/>
@@ -22336,9 +22567,7 @@
       <c r="Q94" s="12"/>
       <c r="R94" s="9"/>
       <c r="S94" s="21"/>
-      <c r="T94" s="17" t="s">
-        <v>72</v>
-      </c>
+      <c r="T94" s="17"/>
       <c r="U94" s="20"/>
       <c r="V94" s="13"/>
       <c r="W94" s="12"/>
@@ -22363,7 +22592,7 @@
       <c r="H95" s="13"/>
       <c r="I95" s="9"/>
       <c r="J95" s="21"/>
-      <c r="K95" s="13"/>
+      <c r="K95" s="17"/>
       <c r="L95" s="20"/>
       <c r="M95" s="13"/>
       <c r="N95" s="12"/>
@@ -22372,18 +22601,18 @@
       <c r="Q95" s="12"/>
       <c r="R95" s="9"/>
       <c r="S95" s="21"/>
-      <c r="T95" s="17"/>
+      <c r="T95" s="17" t="s">
+        <v>72</v>
+      </c>
       <c r="U95" s="20"/>
       <c r="V95" s="13"/>
-      <c r="W95" s="12" t="s">
-        <v>74</v>
-      </c>
+      <c r="W95" s="12"/>
       <c r="X95" s="9"/>
       <c r="Y95" s="21"/>
-      <c r="Z95" s="19"/>
+      <c r="Z95" s="13"/>
       <c r="AA95" s="20"/>
       <c r="AB95" s="13"/>
-      <c r="AC95" s="19"/>
+      <c r="AC95" s="13"/>
       <c r="AD95" s="20"/>
       <c r="AE95" s="13"/>
       <c r="AF95" s="9"/>
@@ -22412,7 +22641,7 @@
       <c r="U96" s="20"/>
       <c r="V96" s="13"/>
       <c r="W96" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X96" s="9"/>
       <c r="Y96" s="21"/>
@@ -22447,13 +22676,15 @@
       <c r="T97" s="17"/>
       <c r="U97" s="20"/>
       <c r="V97" s="13"/>
-      <c r="W97" s="13"/>
+      <c r="W97" s="12" t="s">
+        <v>73</v>
+      </c>
       <c r="X97" s="9"/>
       <c r="Y97" s="21"/>
-      <c r="Z97" s="13"/>
+      <c r="Z97" s="19"/>
       <c r="AA97" s="20"/>
       <c r="AB97" s="13"/>
-      <c r="AC97" s="13"/>
+      <c r="AC97" s="19"/>
       <c r="AD97" s="20"/>
       <c r="AE97" s="13"/>
       <c r="AF97" s="9"/>
@@ -22506,13 +22737,13 @@
       <c r="K99" s="13"/>
       <c r="L99" s="20"/>
       <c r="M99" s="13"/>
-      <c r="N99" s="9"/>
+      <c r="N99" s="12"/>
       <c r="O99" s="9"/>
       <c r="P99" s="21"/>
-      <c r="Q99" s="9"/>
+      <c r="Q99" s="12"/>
       <c r="R99" s="9"/>
       <c r="S99" s="21"/>
-      <c r="T99" s="22"/>
+      <c r="T99" s="17"/>
       <c r="U99" s="20"/>
       <c r="V99" s="13"/>
       <c r="W99" s="13"/>
@@ -22521,9 +22752,7 @@
       <c r="Z99" s="13"/>
       <c r="AA99" s="20"/>
       <c r="AB99" s="13"/>
-      <c r="AC99" s="14" t="s">
-        <v>108</v>
-      </c>
+      <c r="AC99" s="13"/>
       <c r="AD99" s="20"/>
       <c r="AE99" s="13"/>
       <c r="AF99" s="9"/>
@@ -22557,7 +22786,7 @@
       <c r="Z100" s="13"/>
       <c r="AA100" s="20"/>
       <c r="AB100" s="13"/>
-      <c r="AC100" s="13"/>
+      <c r="AC100" s="14"/>
       <c r="AD100" s="20"/>
       <c r="AE100" s="13"/>
       <c r="AF100" s="9"/>
@@ -22591,7 +22820,9 @@
       <c r="Z101" s="13"/>
       <c r="AA101" s="20"/>
       <c r="AB101" s="13"/>
-      <c r="AC101" s="13"/>
+      <c r="AC101" s="14" t="s">
+        <v>108</v>
+      </c>
       <c r="AD101" s="20"/>
       <c r="AE101" s="13"/>
       <c r="AF101" s="9"/>
@@ -22644,7 +22875,7 @@
       <c r="K103" s="13"/>
       <c r="L103" s="20"/>
       <c r="M103" s="13"/>
-      <c r="N103" s="30"/>
+      <c r="N103" s="9"/>
       <c r="O103" s="9"/>
       <c r="P103" s="21"/>
       <c r="Q103" s="9"/>
@@ -22678,7 +22909,7 @@
       <c r="K104" s="13"/>
       <c r="L104" s="20"/>
       <c r="M104" s="13"/>
-      <c r="N104" s="11"/>
+      <c r="N104" s="30"/>
       <c r="O104" s="9"/>
       <c r="P104" s="21"/>
       <c r="Q104" s="9"/>
@@ -22746,7 +22977,7 @@
       <c r="K106" s="13"/>
       <c r="L106" s="20"/>
       <c r="M106" s="13"/>
-      <c r="N106" s="9"/>
+      <c r="N106" s="11"/>
       <c r="O106" s="9"/>
       <c r="P106" s="21"/>
       <c r="Q106" s="9"/>
@@ -22872,34 +23103,34 @@
     <row r="110" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B110" s="9"/>
       <c r="C110" s="9"/>
-      <c r="D110" s="9"/>
-      <c r="E110" s="9"/>
-      <c r="F110" s="9"/>
-      <c r="G110" s="9"/>
-      <c r="H110" s="9"/>
+      <c r="D110" s="21"/>
+      <c r="E110" s="13"/>
+      <c r="F110" s="20"/>
+      <c r="G110" s="13"/>
+      <c r="H110" s="13"/>
       <c r="I110" s="9"/>
-      <c r="J110" s="9"/>
-      <c r="K110" s="9"/>
-      <c r="L110" s="9"/>
-      <c r="M110" s="9"/>
+      <c r="J110" s="21"/>
+      <c r="K110" s="13"/>
+      <c r="L110" s="20"/>
+      <c r="M110" s="13"/>
       <c r="N110" s="9"/>
       <c r="O110" s="9"/>
-      <c r="P110" s="9"/>
+      <c r="P110" s="21"/>
       <c r="Q110" s="9"/>
       <c r="R110" s="9"/>
-      <c r="S110" s="9"/>
-      <c r="T110" s="9"/>
-      <c r="U110" s="9"/>
-      <c r="V110" s="9"/>
-      <c r="W110" s="9"/>
+      <c r="S110" s="21"/>
+      <c r="T110" s="22"/>
+      <c r="U110" s="20"/>
+      <c r="V110" s="13"/>
+      <c r="W110" s="13"/>
       <c r="X110" s="9"/>
-      <c r="Y110" s="9"/>
-      <c r="Z110" s="9"/>
-      <c r="AA110" s="9"/>
-      <c r="AB110" s="9"/>
-      <c r="AC110" s="9"/>
-      <c r="AD110" s="9"/>
-      <c r="AE110" s="9"/>
+      <c r="Y110" s="21"/>
+      <c r="Z110" s="13"/>
+      <c r="AA110" s="20"/>
+      <c r="AB110" s="13"/>
+      <c r="AC110" s="13"/>
+      <c r="AD110" s="20"/>
+      <c r="AE110" s="13"/>
       <c r="AF110" s="9"/>
       <c r="AG110" s="9"/>
     </row>
@@ -22936,6 +23167,40 @@
       <c r="AE111" s="9"/>
       <c r="AF111" s="9"/>
       <c r="AG111" s="9"/>
+    </row>
+    <row r="112" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B112" s="9"/>
+      <c r="C112" s="9"/>
+      <c r="D112" s="9"/>
+      <c r="E112" s="9"/>
+      <c r="F112" s="9"/>
+      <c r="G112" s="9"/>
+      <c r="H112" s="9"/>
+      <c r="I112" s="9"/>
+      <c r="J112" s="9"/>
+      <c r="K112" s="9"/>
+      <c r="L112" s="9"/>
+      <c r="M112" s="9"/>
+      <c r="N112" s="9"/>
+      <c r="O112" s="9"/>
+      <c r="P112" s="9"/>
+      <c r="Q112" s="9"/>
+      <c r="R112" s="9"/>
+      <c r="S112" s="9"/>
+      <c r="T112" s="9"/>
+      <c r="U112" s="9"/>
+      <c r="V112" s="9"/>
+      <c r="W112" s="9"/>
+      <c r="X112" s="9"/>
+      <c r="Y112" s="9"/>
+      <c r="Z112" s="9"/>
+      <c r="AA112" s="9"/>
+      <c r="AB112" s="9"/>
+      <c r="AC112" s="9"/>
+      <c r="AD112" s="9"/>
+      <c r="AE112" s="9"/>
+      <c r="AF112" s="9"/>
+      <c r="AG112" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_concept_6G_integration/MCS_Fall_Detection.xlsx
+++ b/_concept_6G_integration/MCS_Fall_Detection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hayat\Documents\6G\FallDetection_new\_concept_6G_integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA650CF-BBE3-4C6E-9889-3B62ACDAAACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF15102-E15E-49E2-BA99-3255AC721A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="-2970" windowWidth="23232" windowHeight="13872" activeTab="3" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
+    <workbookView xWindow="20544" yWindow="-2970" windowWidth="23232" windowHeight="13872" activeTab="2" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4974,83 +4974,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>185539</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>25053</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>4564</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>101253</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="63" name="Rectangle 62">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F1F71BB-239D-455A-9480-1D1B1E3D79F9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14815939" y="9953465"/>
-          <a:ext cx="1038225" cy="654423"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1">
-            <a:lumMod val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>caregiver DB ??</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1200">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>24</xdr:col>
       <xdr:colOff>131717</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>151856</xdr:rowOff>
@@ -6093,6 +6016,17 @@
               </a:solidFill>
             </a:rPr>
             <a:t>MinIO</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:9002</a:t>
           </a:r>
           <a:endParaRPr lang="en-DE" sz="1200">
             <a:solidFill>
@@ -6825,16 +6759,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>98628</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>486554</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>55262</xdr:rowOff>
+      <xdr:rowOff>48335</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>517728</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>98886</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>133703</xdr:rowOff>
+      <xdr:rowOff>126776</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6849,8 +6783,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10461828" y="5122562"/>
-          <a:ext cx="1028700" cy="649941"/>
+          <a:off x="10240154" y="5174517"/>
+          <a:ext cx="1441132" cy="660332"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6910,7 +6844,18 @@
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>:1883</a:t>
+            <a:t>:1883 (TCP)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:9001 (Websocket)</a:t>
           </a:r>
           <a:endParaRPr lang="en-DE" sz="1200">
             <a:solidFill>
@@ -7955,6 +7900,204 @@
             <a:t>:8001</a:t>
           </a:r>
           <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>148782</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>15292</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>578639</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>94956</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="Rectangle 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E45DC88-B6F5-7A9D-898E-5CCA06D8FB11}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14779182" y="8438856"/>
+          <a:ext cx="1039457" cy="661555"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Postgres</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(fall</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> history)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>148782</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>56856</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>580544</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>136520</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Rectangle 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F2AD9E9-A15A-91E2-E259-DCD22A781E72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14779182" y="9838165"/>
+          <a:ext cx="1041362" cy="661555"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Postgres</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(ml_flow</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1100">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
             </a:solidFill>
@@ -19219,7 +19362,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F5F8DD-066E-404B-880B-D3D7B4214C4F}">
-  <dimension ref="E3:AI49"/>
+  <dimension ref="E3:AI57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="27" max="27" width="4.7109375" customWidth="1"/>
@@ -19885,9 +20028,201 @@
     </row>
     <row r="44" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E44" s="1"/>
-    </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="X44" s="8"/>
+      <c r="Y44" s="8"/>
+      <c r="Z44" s="8"/>
+      <c r="AA44" s="8"/>
+      <c r="AB44" s="8"/>
+      <c r="AC44" s="8"/>
+      <c r="AD44" s="8"/>
+      <c r="AE44" s="8"/>
+      <c r="AF44" s="8"/>
+      <c r="AG44" s="8"/>
+      <c r="AH44" s="8"/>
+      <c r="AI44" s="8"/>
+    </row>
+    <row r="45" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X45" s="8"/>
+      <c r="Y45" s="8"/>
+      <c r="Z45" s="8"/>
+      <c r="AA45" s="8"/>
+      <c r="AB45" s="8"/>
+      <c r="AC45" s="8"/>
+      <c r="AD45" s="8"/>
+      <c r="AE45" s="8"/>
+      <c r="AF45" s="8"/>
+      <c r="AG45" s="8"/>
+      <c r="AH45" s="8"/>
+      <c r="AI45" s="8"/>
+    </row>
+    <row r="46" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X46" s="8"/>
+      <c r="Y46" s="8"/>
+      <c r="Z46" s="8"/>
+      <c r="AA46" s="8"/>
+      <c r="AB46" s="8"/>
+      <c r="AC46" s="8"/>
+      <c r="AD46" s="8"/>
+      <c r="AE46" s="8"/>
+      <c r="AF46" s="8"/>
+      <c r="AG46" s="8"/>
+      <c r="AH46" s="8"/>
+      <c r="AI46" s="8"/>
+    </row>
+    <row r="47" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X47" s="8"/>
+      <c r="Y47" s="8"/>
+      <c r="Z47" s="8"/>
+      <c r="AA47" s="8"/>
+      <c r="AB47" s="8"/>
+      <c r="AC47" s="8"/>
+      <c r="AD47" s="8"/>
+      <c r="AE47" s="8"/>
+      <c r="AF47" s="8"/>
+      <c r="AG47" s="8"/>
+      <c r="AH47" s="8"/>
+      <c r="AI47" s="8"/>
+    </row>
+    <row r="48" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X48" s="8"/>
+      <c r="Y48" s="8"/>
+      <c r="Z48" s="8"/>
+      <c r="AA48" s="8"/>
+      <c r="AB48" s="8"/>
+      <c r="AC48" s="8"/>
+      <c r="AD48" s="8"/>
+      <c r="AE48" s="8"/>
+      <c r="AF48" s="8"/>
+      <c r="AG48" s="8"/>
+      <c r="AH48" s="8"/>
+      <c r="AI48" s="8"/>
+    </row>
+    <row r="49" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E49" s="1"/>
+      <c r="X49" s="8"/>
+      <c r="Y49" s="8"/>
+      <c r="Z49" s="8"/>
+      <c r="AA49" s="8"/>
+      <c r="AB49" s="8"/>
+      <c r="AC49" s="8"/>
+      <c r="AD49" s="8"/>
+      <c r="AE49" s="8"/>
+      <c r="AF49" s="8"/>
+      <c r="AG49" s="8"/>
+      <c r="AH49" s="8"/>
+      <c r="AI49" s="8"/>
+    </row>
+    <row r="50" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X50" s="8"/>
+      <c r="Y50" s="8"/>
+      <c r="Z50" s="8"/>
+      <c r="AA50" s="8"/>
+      <c r="AB50" s="8"/>
+      <c r="AC50" s="8"/>
+      <c r="AD50" s="8"/>
+      <c r="AE50" s="8"/>
+      <c r="AF50" s="8"/>
+      <c r="AG50" s="8"/>
+      <c r="AH50" s="8"/>
+      <c r="AI50" s="8"/>
+    </row>
+    <row r="51" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X51" s="8"/>
+      <c r="Y51" s="8"/>
+      <c r="Z51" s="8"/>
+      <c r="AA51" s="8"/>
+      <c r="AB51" s="8"/>
+      <c r="AC51" s="8"/>
+      <c r="AD51" s="8"/>
+      <c r="AE51" s="8"/>
+      <c r="AF51" s="8"/>
+      <c r="AG51" s="8"/>
+      <c r="AH51" s="8"/>
+      <c r="AI51" s="8"/>
+    </row>
+    <row r="52" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X52" s="8"/>
+      <c r="Y52" s="8"/>
+      <c r="Z52" s="8"/>
+      <c r="AA52" s="8"/>
+      <c r="AB52" s="8"/>
+      <c r="AC52" s="8"/>
+      <c r="AD52" s="8"/>
+      <c r="AE52" s="8"/>
+      <c r="AF52" s="8"/>
+      <c r="AG52" s="8"/>
+      <c r="AH52" s="8"/>
+      <c r="AI52" s="8"/>
+    </row>
+    <row r="53" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X53" s="8"/>
+      <c r="Y53" s="8"/>
+      <c r="Z53" s="8"/>
+      <c r="AA53" s="8"/>
+      <c r="AB53" s="8"/>
+      <c r="AC53" s="8"/>
+      <c r="AD53" s="8"/>
+      <c r="AE53" s="8"/>
+      <c r="AF53" s="8"/>
+      <c r="AG53" s="8"/>
+      <c r="AH53" s="8"/>
+      <c r="AI53" s="8"/>
+    </row>
+    <row r="54" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X54" s="8"/>
+      <c r="Y54" s="8"/>
+      <c r="Z54" s="8"/>
+      <c r="AA54" s="8"/>
+      <c r="AB54" s="8"/>
+      <c r="AC54" s="8"/>
+      <c r="AD54" s="8"/>
+      <c r="AE54" s="8"/>
+      <c r="AF54" s="8"/>
+      <c r="AG54" s="8"/>
+      <c r="AH54" s="8"/>
+      <c r="AI54" s="8"/>
+    </row>
+    <row r="55" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X55" s="8"/>
+      <c r="Y55" s="8"/>
+      <c r="Z55" s="8"/>
+      <c r="AA55" s="8"/>
+      <c r="AB55" s="8"/>
+      <c r="AC55" s="8"/>
+      <c r="AD55" s="8"/>
+      <c r="AE55" s="8"/>
+      <c r="AF55" s="8"/>
+      <c r="AG55" s="8"/>
+      <c r="AH55" s="8"/>
+      <c r="AI55" s="8"/>
+    </row>
+    <row r="56" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X56" s="8"/>
+      <c r="Y56" s="8"/>
+      <c r="Z56" s="8"/>
+      <c r="AA56" s="8"/>
+      <c r="AB56" s="8"/>
+      <c r="AC56" s="8"/>
+      <c r="AD56" s="8"/>
+      <c r="AE56" s="8"/>
+      <c r="AF56" s="8"/>
+      <c r="AG56" s="8"/>
+      <c r="AH56" s="8"/>
+      <c r="AI56" s="8"/>
+    </row>
+    <row r="57" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X57" s="8"/>
+      <c r="Y57" s="8"/>
+      <c r="Z57" s="8"/>
+      <c r="AA57" s="8"/>
+      <c r="AB57" s="8"/>
+      <c r="AC57" s="8"/>
+      <c r="AD57" s="8"/>
+      <c r="AE57" s="8"/>
+      <c r="AF57" s="8"/>
+      <c r="AG57" s="8"/>
+      <c r="AH57" s="8"/>
+      <c r="AI57" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/_concept_6G_integration/MCS_Fall_Detection.xlsx
+++ b/_concept_6G_integration/MCS_Fall_Detection.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hayat\Documents\6G\FallDetection_new\_concept_6G_integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8651ACD-0131-4B99-BB08-1B3D836AF2BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862AC03C-A186-4933-89C3-6974FDE1CC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="-2970" windowWidth="23232" windowHeight="13872" activeTab="2" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
+    <workbookView xWindow="20544" yWindow="-2970" windowWidth="23232" windowHeight="13872" firstSheet="1" activeTab="2" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Architecture" sheetId="3" r:id="rId1"/>
-    <sheet name="SequenceDiagram" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId3"/>
-    <sheet name="SequenceDiagram (2)" sheetId="5" state="hidden" r:id="rId4"/>
+    <sheet name="Architecture (2)" sheetId="7" state="hidden" r:id="rId1"/>
+    <sheet name="Architecture" sheetId="3" r:id="rId2"/>
+    <sheet name="SequenceDiagram" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
+    <sheet name="SequenceDiagram (2)" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="87">
   <si>
     <t xml:space="preserve">Additional Components </t>
   </si>
@@ -277,12 +278,51 @@
   <si>
     <t xml:space="preserve"> 4. ToDos</t>
   </si>
+  <si>
+    <t xml:space="preserve">ml model health mtrics </t>
+  </si>
+  <si>
+    <t>data displayed on fall dashbaord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model peformance metrics per ver during training </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecepriment/run ID </t>
+  </si>
+  <si>
+    <t xml:space="preserve">model versions </t>
+  </si>
+  <si>
+    <t>logs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alert time </t>
+  </si>
+  <si>
+    <t xml:space="preserve">patient confirmed or nor </t>
+  </si>
+  <si>
+    <t>need help ior not</t>
+  </si>
+  <si>
+    <t>observation ID</t>
+  </si>
+  <si>
+    <t>Data comes from infrence API</t>
+  </si>
+  <si>
+    <t>MLflow tracking server</t>
+  </si>
+  <si>
+    <t>fall_dashboard background task</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -366,6 +406,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -435,7 +488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -484,6 +537,11 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -502,6 +560,5358 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>219299</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>94130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>353738</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>168762</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B25D8373-2EBC-4E74-A3AF-252D110396D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1440404" y="3827930"/>
+          <a:ext cx="11107239" cy="4646632"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="dash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>16363</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>71044</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>270511</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>183103</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA9EE178-0DE6-4CD4-B274-453850AE5A18}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2454763" y="263449"/>
+          <a:ext cx="5740548" cy="2893359"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="dash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>416635</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>121136</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>214705</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>155426</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{145D7699-5A8C-4CC2-B0BC-1A97F4B164D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="416635" y="1285091"/>
+          <a:ext cx="1019175" cy="664845"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SamrKo</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>43253</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>471207</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rectangle 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C433D5D-9831-4B27-AA20-B356D4FD7D5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2483558" y="102758"/>
+          <a:ext cx="1037554" cy="278242"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Mobile App</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>29963</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>35170</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>94129</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>69141</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangle 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91965B72-84BE-4B0E-B082-7F043AE04A21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1860668" y="4340470"/>
+          <a:ext cx="1891061" cy="226376"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Unchangeable Component</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>431202</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>178957</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>502023</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>22411</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectangle 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE4710B2-0955-4AA0-B779-A51EF056ECDF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9577107" y="2177302"/>
+          <a:ext cx="680421" cy="233979"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>240477</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>96371</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>63312</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>5938</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Rectangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FAD90B0-CE35-431C-B20A-A545F6823CDA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1461582" y="3639671"/>
+          <a:ext cx="1042035" cy="292472"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Backend</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>409016</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>459442</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Rectangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F5A0C6F-A1C8-4F53-BD54-29D0DACF8019}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9554921" y="1773779"/>
+          <a:ext cx="658121" cy="232186"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>235323</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>165932</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>65079</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Rectangle 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E24922D-9BAD-40E3-9BC1-EF34A1530754}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1456428" y="9235637"/>
+          <a:ext cx="10087872" cy="1613647"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>420221</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>177140</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>219808</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>117524</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Rectangle 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7F7167C-A636-4F68-A082-8079FBD2162A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1639421" y="9056345"/>
+          <a:ext cx="1630292" cy="319479"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Web App / Browser</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>413117</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>82949</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>235953</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>159149</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Rectangle 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A36121CC-2208-450D-AB36-E2067B283349}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8949422" y="9914654"/>
+          <a:ext cx="1042036" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Dashboard</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(Syste</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>m Health</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>255631</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>108205</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>234461</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>184405</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Rectangle 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0103695-5FEB-4661-8B20-C8D812152F2D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4524736" y="9939910"/>
+          <a:ext cx="1198030" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Pat Dashboard</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(patient monitoring)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1000">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>246529</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>14654</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>372036</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>155287</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Rectangle 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DD70C63-8CE2-4B46-A0D6-A0368661C863}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7561729" y="9463454"/>
+          <a:ext cx="3785012" cy="1283633"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="dash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>556845</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>14654</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>513231</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>150805</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Rectangle 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFA26218-030D-4F7C-B303-8B5E73B58799}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4214445" y="9463454"/>
+          <a:ext cx="3004386" cy="1279151"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="dash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>168380</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>166089</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>322384</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>27023</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Rectangle 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F316476A-951E-461E-8E2B-0981880C9164}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5045180" y="9616794"/>
+          <a:ext cx="1373204" cy="241934"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" b="1" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Caregiver User</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>222169</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>113505</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>446287</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>167180</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Rectangle 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{930F7173-C8AA-45A3-9072-567C5138D542}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8758474" y="9562305"/>
+          <a:ext cx="1443318" cy="244175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" b="1" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Admin User</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>353037</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>96138</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>175873</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>172338</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Rectangle 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A89A36C6-E7D5-4A66-8204-C715C54A79A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10108542" y="9925938"/>
+          <a:ext cx="1040131" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Dashboard</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(ml monitoring)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>484922</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>96137</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>307757</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>172337</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Rectangle 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D4EC92A-28FC-495D-A364-5637DF124645}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7802027" y="9925937"/>
+          <a:ext cx="1040130" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>/Doc</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>378722</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>114067</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>357553</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>190267</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Rectangle 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{731FDE0A-2123-44F0-A330-EF578C554652}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5865122" y="9943867"/>
+          <a:ext cx="1198031" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Fall Dashboard</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(fall</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> history + alert</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1000">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>279475</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>49530</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>61129</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="21" name="Straight Arrow Connector 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3A92D77-75B0-4471-B9F0-0405BBBF7CFB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1500580" y="1644015"/>
+          <a:ext cx="899720" cy="9694"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>80179</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>327100</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="Straight Arrow Connector 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3470ADFF-CB26-42F9-8897-E7C4BC4AF7D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5200650" y="3242479"/>
+          <a:ext cx="3250" cy="481796"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>179239</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>369010</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="Straight Arrow Connector 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8A2DB35-7C18-4DB2-B6D7-2D0839675D4F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5242560" y="8677444"/>
+          <a:ext cx="5155" cy="481796"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>138792</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>191315</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>557892</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>77015</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Rectangle 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16AA0C98-7320-403E-8B06-E97961FF1C0A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="29108127" y="9259115"/>
+          <a:ext cx="1028700" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="10000"/>
+            <a:lumOff val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MQTT</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> Client 3</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(influx writer)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>113755</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>191588</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>532855</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>77288</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="Rectangle 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FA6D363-7B23-410C-9FD3-2513EEC4FB87}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="29081185" y="8497388"/>
+          <a:ext cx="1028700" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="10000"/>
+            <a:lumOff val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MQTT</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> Client 4</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(alert manager)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>508315</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>130629</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>87086</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>128644</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="Rectangle 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF2D11F7-3472-4BCA-92BE-38CC1A51626C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7215820" y="6340929"/>
+          <a:ext cx="3845971" cy="1712515"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="10000"/>
+            <a:lumOff val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>94609</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>4019</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>514381</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>77977</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Rectangle 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93EEC2EE-B7AE-4812-83A1-DB83EE9B4287}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7409809" y="6404819"/>
+          <a:ext cx="1029372" cy="645458"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Grafana </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:3000</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>102198</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>70149</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>521970</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>148253</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Rectangle 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4DCCFEF-FABC-47C3-8137-60B6F9CE7898}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8638503" y="7234854"/>
+          <a:ext cx="1029372" cy="647699"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MLFlow</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:5000</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>436583</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>5442</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>168330</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>110761</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Rectangle 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3EFC9E9-8E4A-4F06-9137-DD2CBCAFEF94}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10190183" y="4884147"/>
+          <a:ext cx="1560547" cy="1246414"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="10000"/>
+            <a:lumOff val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>131717</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>151856</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>554627</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>37556</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="Rectangle 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DF306CF-8581-4FE2-9CAF-352424C2575C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14762117" y="3314156"/>
+          <a:ext cx="1032510" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>caregiver DB</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>127908</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>40005</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>548913</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Rectangle 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1DD5BB0-90C5-423D-AFC5-AFEE0832D6B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14760213" y="2036445"/>
+          <a:ext cx="1028700" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>InfluxDB</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>149679</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>44632</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>572589</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>120832</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="Rectangle 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43310445-5ABE-4106-A206-E3ADD2B5A76D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14780079" y="4542337"/>
+          <a:ext cx="1032510" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FHIR</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> DB</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>146877</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>174620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>576734</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>60320</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="Rectangle 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD2AC4DC-5FE5-4864-B609-0CD80FC05727}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14779182" y="5622920"/>
+          <a:ext cx="1039457" cy="647700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Postgres</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(inference</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> log)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>548289</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>163285</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>490129</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Rectangle 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73DAB4F6-A200-4C7F-89C5-B74AE6B8F2A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6034689" y="355690"/>
+          <a:ext cx="1772545" cy="2692309"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="10000"/>
+            <a:lumOff val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>281955</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>53954</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>85068</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>141320</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="Rectangle 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B63C6C42-710C-4C6D-9702-7A04E7644942}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6377955" y="1216004"/>
+          <a:ext cx="1024218" cy="721731"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Messenger</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>282420</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>101735</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>91920</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>579890</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Rectangle 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF488DCC-B127-4C5B-84F5-DEFC6CEA195B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6378420" y="484640"/>
+          <a:ext cx="1028700" cy="668655"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MQTT Client</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 1</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(alert messenger)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="900">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>240046</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>82541</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>46969</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>177791</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="Rectangle 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB362A54-DF8D-4A08-AC5E-DAC5E40916CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6337951" y="2080886"/>
+          <a:ext cx="1026123" cy="678180"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Patient input confirmation</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>279954</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>206827</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>3265</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="Rectangle 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A133B256-F40B-4BEA-8B17-59B756BE3299}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2720259" y="419100"/>
+          <a:ext cx="2972968" cy="2555965"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="10000"/>
+            <a:lumOff val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>392896</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>38806</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>202395</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>137418</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="Rectangle 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22DB0884-B57E-4C73-A16E-722FBFE887C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2833201" y="2035246"/>
+          <a:ext cx="1028699" cy="681542"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Influx Writer</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>195943</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>110490</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Rectangle 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05C6FE9C-DD69-4672-93BB-59BCDA248CCA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2868930" y="769348"/>
+          <a:ext cx="1032510" cy="693692"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Data Collector</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>501273</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>4318</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>310773</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>137192</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="Rectangle 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5C7FC78-0D7D-4380-89E2-E82F894FA149}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4160778" y="2000758"/>
+          <a:ext cx="1028700" cy="715804"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>API caller</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>78472</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>52669</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>498244</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>128870</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="Rectangle 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A4C90E1-8EE2-4C8F-8580-E5CADB8CE4EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9832072" y="7215469"/>
+          <a:ext cx="1029372" cy="647701"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="0070C0"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MinIO</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:9002</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>433107</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>189827</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>503928</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>40340</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="Rectangle 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA9C7BD7-1D32-4039-ADCF-53CDFBB17102}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9579012" y="2578697"/>
+          <a:ext cx="680421" cy="242943"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="0070C0"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>179293</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>24317</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>602875</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>100518</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="Rectangle 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3553EDF-1094-425E-A969-D0D9DAD12BD4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14811598" y="6998522"/>
+          <a:ext cx="1033182" cy="647701"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="0070C0"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MinIO</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>191348</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>63809</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>9700</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>140346</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="Rectangle 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DE83DC2-EDDB-45EE-A610-8D05D30250D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8725748" y="6466514"/>
+          <a:ext cx="1039457" cy="648037"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Postgres</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MLflow</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:5432</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>66114</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>7845</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>491601</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>84044</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="Rectangle 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2415F92-BE98-4E3E-B286-94AC4CB4D00D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7383219" y="7172550"/>
+          <a:ext cx="1033182" cy="647699"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Prometeheus</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:9090</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>20732</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>447563</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>30703</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="Rectangle 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D6EED93-B8BC-4355-87CA-8B471109CA31}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5507132" y="4648200"/>
+          <a:ext cx="1647936" cy="3309208"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="10000"/>
+            <a:lumOff val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>244176</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>36546</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>515471</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="Rectangle 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60F45C85-10D2-45F2-B5F4-B18C6EF32454}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2072976" y="4722846"/>
+          <a:ext cx="3319295" cy="2706654"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="10000"/>
+            <a:lumOff val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>269742</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>50843</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>285815</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>11862</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="Rectangle 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EE8976E-318A-4993-93AF-10CCF14AD5C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5756142" y="5501048"/>
+          <a:ext cx="1235273" cy="723019"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Postgres</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="700" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>inference_log + fall_history</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:5432</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>340131</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>70067</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>149631</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>146268</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="Rectangle 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{329AFE24-33EC-4AB6-B457-2588C54B9FCF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5826531" y="4758272"/>
+          <a:ext cx="1028700" cy="647701"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MQTT</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> Client 2</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(alert displayer)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>486554</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>48335</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>98886</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>126776</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="Rectangle 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D9D3DBE-4334-49E7-832B-5D4F60FFDEBF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10242059" y="5117540"/>
+          <a:ext cx="1439227" cy="649941"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MQTT</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> Broker</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:1883 (TCP)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:9001 (Websocket)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>166934</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>67418</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>571674</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>138249</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="Rectangle 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBD59FF0-FD21-4669-B96B-A5D6B58F98D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5653334" y="7041623"/>
+          <a:ext cx="1014340" cy="832831"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>fall</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>dashboard </a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:8002</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="800" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>346274</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>162474</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>381559</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>27512</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="Rectangle 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{011EEE99-8116-4D91-8773-4860FBD73925}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4003874" y="5612679"/>
+          <a:ext cx="1254485" cy="627038"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Pat Dahboard backgroundTasks</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(data fecther etc.) </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1200" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>106119</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>185809</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>529029</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>71510</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="Rectangle 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8CF8306-0D22-4D35-94AB-1CC792D7D5AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2546424" y="5062609"/>
+          <a:ext cx="1030605" cy="647701"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FHIR</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> DB</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>580128</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>110490</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>201705</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>148443</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="Rectangle 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7C9A7B2-7BB5-477C-A1F7-88014A0CF735}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1801233" y="4225290"/>
+          <a:ext cx="2059977" cy="3276453"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>20968</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>51089</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>425708</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>116541</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="Rectangle 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFBFC799-6CDE-4026-A8B8-CAB8D8960463}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2459368" y="6072794"/>
+          <a:ext cx="1016245" cy="825547"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Patient</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>dashboard </a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:????</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="800" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>295835</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>129539</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>392159</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>17929</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="57" name="Rectangle 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F54AA5D-D1E9-4113-A38C-43BC2351C663}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3955340" y="4244339"/>
+          <a:ext cx="8021124" cy="3888890"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="dash"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>270700</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>91701</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>307890</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>149479</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="Rectangle 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31019F0D-7406-4D27-AA10-855DB49406EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5757100" y="6302001"/>
+          <a:ext cx="1256390" cy="629278"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>fall Dahboard backgroundTasks</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(data fecther etc.) </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1200" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>537882</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>156881</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>277233</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>165847</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="59" name="Rectangle 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{715C8C01-FBF9-423E-B392-EAAF374DB6CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7243482" y="4652681"/>
+          <a:ext cx="2789256" cy="1534871"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="10000"/>
+            <a:lumOff val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>589733</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>23400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>165190</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>70756</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="Rectangle 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08DB2A79-7D53-4F6B-A26D-AB4FF923CBAA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4247333" y="4328700"/>
+          <a:ext cx="7502162" cy="239761"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Changeable Component</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:srgbClr val="002060"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>317129</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>86735</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>130439</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>166743</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="61" name="Rectangle 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E1F949D-48B9-4F19-A18E-F795CF860ED6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8853434" y="4774940"/>
+          <a:ext cx="1030605" cy="649603"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>InfluxDB</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>6948</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>80028</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>429857</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>158132</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="62" name="Rectangle 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A7F7F8A-5213-47AC-9B7B-463A856C1A2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7324053" y="4766328"/>
+          <a:ext cx="1032509" cy="651509"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Data Preprocessor</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>27087</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18157</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>451901</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>94356</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="63" name="Rectangle 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7064B41A-640C-4DEC-8532-A610A47C05D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7953792" y="5466457"/>
+          <a:ext cx="1034414" cy="647699"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Inference</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>API server</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:8001</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>148782</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>15292</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>578639</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>94956</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="64" name="Rectangle 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5FE2DC3-D50F-4EB4-BBFE-47AF8A6D196A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14779182" y="8321092"/>
+          <a:ext cx="1041362" cy="651164"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Postgres</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(fall</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> history)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>148782</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>56856</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>580544</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>136520</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="65" name="Rectangle 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC860363-7811-42F2-8DFA-17A76B53060D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14779182" y="9696156"/>
+          <a:ext cx="1043267" cy="651164"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Postgres</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(ml_flow</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1804,6 +7214,17 @@
             </a:rPr>
             <a:t>(ml monitoring)</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:8004</a:t>
+          </a:r>
           <a:endParaRPr lang="en-DE" sz="1050">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
@@ -1882,7 +7303,7 @@
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>/Doc</a:t>
+            <a:t>8001/Doc</a:t>
           </a:r>
           <a:endParaRPr lang="en-DE" sz="1050">
             <a:solidFill>
@@ -1990,6 +7411,17 @@
               </a:solidFill>
             </a:rPr>
             <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:8002</a:t>
           </a:r>
           <a:endParaRPr lang="en-DE" sz="1000">
             <a:solidFill>
@@ -2377,16 +7809,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>508315</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>130629</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>487904</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>121648</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>87086</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>129315</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>128644</xdr:rowOff>
+      <xdr:rowOff>141514</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2401,8 +7833,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7213915" y="6340929"/>
-          <a:ext cx="3845971" cy="1712515"/>
+          <a:off x="5974304" y="6522448"/>
+          <a:ext cx="3908611" cy="1543866"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2458,16 +7890,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>94609</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>4019</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>92032</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>123747</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>514381</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>77977</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>509899</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>7204</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2482,8 +7914,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7409809" y="6404819"/>
-          <a:ext cx="1029372" cy="645458"/>
+          <a:off x="6188032" y="6715047"/>
+          <a:ext cx="1027467" cy="645457"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2545,15 +7977,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>102198</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>70149</xdr:rowOff>
+      <xdr:colOff>36868</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>109193</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>521970</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>148253</xdr:rowOff>
+      <xdr:colOff>456640</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>185392</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2568,8 +8000,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8636598" y="7300184"/>
-          <a:ext cx="1029372" cy="656328"/>
+          <a:off x="8571268" y="6700493"/>
+          <a:ext cx="1029372" cy="647699"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2610,7 +8042,7 @@
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>MLFlow</a:t>
+            <a:t>mlflow</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2636,15 +8068,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>436583</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>5442</xdr:rowOff>
+      <xdr:colOff>363071</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>102710</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>168330</xdr:colOff>
+      <xdr:colOff>275235</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>110761</xdr:rowOff>
+      <xdr:rowOff>9573</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2659,8 +8091,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10190183" y="4882242"/>
-          <a:ext cx="1560547" cy="1248319"/>
+          <a:off x="10116671" y="4827110"/>
+          <a:ext cx="1740964" cy="1256051"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2747,8 +8179,17 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx1"/>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
         </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -3692,97 +9133,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>78472</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>52669</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>498244</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>128870</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="73" name="Rectangle 72">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E205DCDE-450E-485B-AE7A-DAA82806602A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9832072" y="7215469"/>
-          <a:ext cx="1029372" cy="647701"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:sysClr val="window" lastClr="FFFFFF"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="0070C0"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:srgbClr val="0070C0"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>MinIO</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:srgbClr val="0070C0"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>:9002</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1200">
-            <a:solidFill>
-              <a:srgbClr val="0070C0"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>433107</xdr:colOff>
       <xdr:row>10</xdr:row>
@@ -3935,23 +9285,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>191348</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>63809</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>68019</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>85950</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>9700</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>140346</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>491601</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>162149</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="76" name="Rectangle 75">
+        <xdr:cNvPr id="77" name="Rectangle 76">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4CBDEC7-0CCD-41BD-A0F7-CA9F10F332C6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E6DD959-4E17-4FCC-B702-14DE2252E107}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3959,8 +9309,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8725748" y="6522880"/>
-          <a:ext cx="1037552" cy="654760"/>
+          <a:off x="7383219" y="6677250"/>
+          <a:ext cx="1033182" cy="647699"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3996,56 +9346,24 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-GB" sz="1200">
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>Postgres</a:t>
+            <a:t>Prometeheus</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-GB" sz="1100">
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1050">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>MLflow</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>:5432</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
+            <a:t>:9090</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4053,23 +9371,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>66114</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>7845</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>244176</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>36546</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>491601</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>84044</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>403412</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="77" name="Rectangle 76">
+        <xdr:cNvPr id="19" name="Rectangle 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E6DD959-4E17-4FCC-B702-14DE2252E107}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E31A638-4D14-42B6-86ED-BD4671D3EC00}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4077,94 +9395,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7381314" y="7237880"/>
-          <a:ext cx="1035087" cy="654423"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="002060"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="002060"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Prometeheus</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>:9090</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>20732</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>447563</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>30703</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="Rectangle 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4AAFE0D-0416-44FE-9662-765A330E3412}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5507132" y="4648200"/>
-          <a:ext cx="1646031" cy="3307303"/>
+          <a:off x="2072976" y="4760946"/>
+          <a:ext cx="3816836" cy="2738030"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4220,199 +9452,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>244176</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>36546</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>456000</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>11124</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>515471</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="Rectangle 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E31A638-4D14-42B6-86ED-BD4671D3EC00}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2072976" y="4760946"/>
-          <a:ext cx="3319295" cy="2738030"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="10000"/>
-            <a:lumOff val="90000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="en-GB" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="en-DE" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>269742</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>50843</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>285815</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>11862</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="Rectangle 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB419F36-7831-4631-AD43-8C71165FF4DC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5756142" y="5499143"/>
-          <a:ext cx="1235273" cy="723019"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="002060"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="002060"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Postgres</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="700" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>inference_log + fall_history</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>:5432</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>340131</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>70067</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>149631</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>146268</xdr:rowOff>
+      <xdr:colOff>265500</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>87326</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4427,8 +9476,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5826531" y="4756367"/>
-          <a:ext cx="1028700" cy="647701"/>
+          <a:off x="4113600" y="6662936"/>
+          <a:ext cx="1028700" cy="654425"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4612,122 +9661,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>166934</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>67418</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>571674</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>138249</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="72" name="Rectangle 71">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63B17D3D-D374-4205-80CD-24266A83C401}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5653334" y="7039718"/>
-          <a:ext cx="1014340" cy="832831"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="002060"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="002060"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>fall</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>dashboard </a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>:8002</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-GB" sz="800" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>346274</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>162474</xdr:rowOff>
+      <xdr:colOff>462815</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>157319</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>381559</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>27512</xdr:rowOff>
+      <xdr:colOff>498100</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>22356</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4742,7 +9685,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4003874" y="5657839"/>
+          <a:off x="4120415" y="5074460"/>
           <a:ext cx="1254485" cy="636002"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4784,22 +9727,7 @@
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>Pat Dahboard backgroundTasks</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-GB" sz="900" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(data fecther etc.) </a:t>
+            <a:t>web app backgroundTasks</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1200" baseline="0">
             <a:solidFill>
@@ -4882,7 +9810,7 @@
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t> DB</a:t>
+            <a:t> server</a:t>
           </a:r>
           <a:endParaRPr lang="en-DE" sz="1200">
             <a:solidFill>
@@ -5143,16 +10071,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>270700</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>91701</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>424333</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>171712</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>307890</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>149479</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>461523</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>40559</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5167,8 +10095,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5757100" y="6302001"/>
-          <a:ext cx="1256390" cy="629278"/>
+          <a:off x="4081933" y="5859818"/>
+          <a:ext cx="1256390" cy="639812"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5209,22 +10137,15 @@
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>fall Dahboard backgroundTasks</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
+            <a:t>web app backgroundTasks</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="900" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-GB" sz="900" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(data fecther etc.) </a:t>
+            <a:t> </a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1200" baseline="0">
             <a:solidFill>
@@ -5238,16 +10159,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>537882</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>156881</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>322729</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>40340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>277233</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>165847</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>63985</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>51210</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5262,8 +10183,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7243482" y="4688540"/>
-          <a:ext cx="2787351" cy="1550895"/>
+          <a:off x="6418729" y="4957481"/>
+          <a:ext cx="2789256" cy="1552800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5397,16 +10318,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>317129</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>86735</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>34068</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>99509</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>130439</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>166743</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>455073</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>177613</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5421,8 +10342,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8851529" y="4811135"/>
-          <a:ext cx="1032510" cy="658232"/>
+          <a:off x="6739668" y="5402133"/>
+          <a:ext cx="1030605" cy="656327"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5472,96 +10393,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>6948</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>80028</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>429857</xdr:colOff>
+      <xdr:colOff>55886</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>158132</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="Rectangle 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D97889AF-DA54-4A0E-AB55-FF0B0E7A031A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7322148" y="4804428"/>
-          <a:ext cx="1032509" cy="656328"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="002060"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Data Preprocessor</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1200">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>27087</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>18157</xdr:rowOff>
+      <xdr:rowOff>112285</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>451901</xdr:colOff>
+      <xdr:colOff>480700</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>94356</xdr:rowOff>
+      <xdr:rowOff>103414</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5576,8 +10417,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7951887" y="5513522"/>
-          <a:ext cx="1034414" cy="654422"/>
+          <a:off x="7980686" y="5370085"/>
+          <a:ext cx="1034414" cy="753129"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5850,30 +10691,25 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>499141</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>66482</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>363071</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>16873</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>321704</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>46196</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>282855</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>53787</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="Rectangle 14">
+        <xdr:cNvPr id="25" name="Rectangle 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45D33074-E4A0-EFB9-8175-A845D9761FDC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E96DA50-B312-4E58-8743-838458F6A913}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5881,15 +10717,16 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7204741" y="22038976"/>
-          <a:ext cx="7137763" cy="557938"/>
+          <a:off x="10116671" y="6283202"/>
+          <a:ext cx="1748584" cy="1771585"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="bg1">
-            <a:lumMod val="95000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="10000"/>
+            <a:lumOff val="90000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:ln>
@@ -5917,156 +10754,17 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Mobile app direclty writes</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-GB">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Fall confirmed @ HH:MM:SSS </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1400" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>/</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Help requested @ HH:MM:SSS </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1400" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>/</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>No Reponse @ HH:MM:SSS</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1050" b="0">
+          <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="85000"/>
-                <a:lumOff val="15000"/>
-              </a:schemeClr>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -6074,6 +10772,429 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>195013</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>85949</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>7090</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>162150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="73" name="Rectangle 72">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E205DCDE-450E-485B-AE7A-DAA82806602A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10558213" y="7315984"/>
+          <a:ext cx="1031277" cy="654425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="0070C0"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MinIO</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:9002</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>110842</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>166040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>125010</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>127058</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Rectangle 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB419F36-7831-4631-AD43-8C71165FF4DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10474042" y="6432369"/>
+          <a:ext cx="1233368" cy="731983"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Postgres</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:5432</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>73734</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>105319</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>493506</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>29887</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Rectangle 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E1A4619-421A-4377-A170-5E2FA4454A89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7388934" y="7458619"/>
+          <a:ext cx="1029372" cy="496068"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Prome TSDB</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>202730</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>67491</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>12902</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>97970</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Rectangle 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1C32DD4-9822-57B6-48BE-4CFDFDC4F1B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14833130" y="10849791"/>
+          <a:ext cx="1029372" cy="601979"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Prome TSDB</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(90D retention)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>148782</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>138499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>582449</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>27663</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="Rectangle 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A15B901-6A5C-F296-6CE5-E441F9B807B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14779182" y="11873299"/>
+          <a:ext cx="1043267" cy="651164"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="002060"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MQTT broker </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -12504,7 +17625,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -16833,7 +21954,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F5F8DD-066E-404B-880B-D3D7B4214C4F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CA1E940-7BBC-4781-99CE-08F496819A6E}">
   <dimension ref="E3:AI57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16888,18 +22009,18 @@
     </row>
     <row r="6" spans="18:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="X6" s="3"/>
-      <c r="Y6" s="25" t="s">
+      <c r="Y6" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="Z6" s="25"/>
-      <c r="AA6" s="25" t="s">
+      <c r="Z6" s="26"/>
+      <c r="AA6" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="AB6" s="25"/>
-      <c r="AC6" s="25"/>
-      <c r="AD6" s="20"/>
-      <c r="AE6" s="20"/>
-      <c r="AF6" s="20"/>
+      <c r="AB6" s="26"/>
+      <c r="AC6" s="26"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="25"/>
       <c r="AG6" s="22" t="s">
         <v>44</v>
       </c>
@@ -17698,6 +22819,1071 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AA6:AC6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F5F8DD-066E-404B-880B-D3D7B4214C4F}">
+  <dimension ref="E3:AI69"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="27" max="27" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="18:35" x14ac:dyDescent="0.25">
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
+    </row>
+    <row r="4" spans="18:35" ht="46.5" x14ac:dyDescent="0.7">
+      <c r="X4" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y4" s="19"/>
+      <c r="Z4" s="19"/>
+      <c r="AA4" s="19"/>
+      <c r="AB4" s="19"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="3"/>
+    </row>
+    <row r="5" spans="18:35" x14ac:dyDescent="0.25">
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
+      <c r="AG5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH5" s="3"/>
+      <c r="AI5" s="3"/>
+    </row>
+    <row r="6" spans="18:35" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="X6" s="3"/>
+      <c r="Y6" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z6" s="26"/>
+      <c r="AA6" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB6" s="26"/>
+      <c r="AC6" s="26"/>
+      <c r="AD6" s="20"/>
+      <c r="AE6" s="20"/>
+      <c r="AF6" s="20"/>
+      <c r="AG6" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="3"/>
+    </row>
+    <row r="7" spans="18:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="X7" s="3"/>
+      <c r="Y7" s="21"/>
+      <c r="Z7" s="21"/>
+      <c r="AA7" s="21"/>
+      <c r="AB7" s="21"/>
+      <c r="AC7" s="21"/>
+      <c r="AD7" s="21"/>
+      <c r="AE7" s="21"/>
+      <c r="AF7" s="21"/>
+      <c r="AG7" s="21"/>
+      <c r="AH7" s="3"/>
+      <c r="AI7" s="3"/>
+    </row>
+    <row r="8" spans="18:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="3"/>
+      <c r="AI8" s="3"/>
+    </row>
+    <row r="9" spans="18:35" x14ac:dyDescent="0.25">
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH9" s="3"/>
+      <c r="AI9" s="3"/>
+    </row>
+    <row r="10" spans="18:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH10" s="3"/>
+      <c r="AI10" s="3"/>
+    </row>
+    <row r="11" spans="18:35" x14ac:dyDescent="0.25">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="18:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="R12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="3"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH12" s="3"/>
+      <c r="AI12" s="3"/>
+    </row>
+    <row r="13" spans="18:35" x14ac:dyDescent="0.25">
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="3"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="3"/>
+      <c r="AG13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH13" s="3"/>
+      <c r="AI13" s="3"/>
+    </row>
+    <row r="14" spans="18:35" x14ac:dyDescent="0.25">
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="3"/>
+      <c r="AD14" s="3"/>
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="3"/>
+      <c r="AG14" s="3"/>
+      <c r="AH14" s="3"/>
+      <c r="AI14" s="3"/>
+    </row>
+    <row r="15" spans="18:35" x14ac:dyDescent="0.25">
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3"/>
+      <c r="AH15" s="3"/>
+      <c r="AI15" s="3"/>
+    </row>
+    <row r="16" spans="18:35" x14ac:dyDescent="0.25">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC16" s="28"/>
+      <c r="AD16" s="28"/>
+      <c r="AE16" s="28"/>
+      <c r="AF16" s="28"/>
+      <c r="AG16" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC17" s="28"/>
+      <c r="AD17" s="28"/>
+      <c r="AE17" s="28"/>
+      <c r="AF17" s="28"/>
+      <c r="AG17" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH17" s="3"/>
+      <c r="AI17" s="3"/>
+    </row>
+    <row r="18" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC18" s="28"/>
+      <c r="AD18" s="28"/>
+      <c r="AE18" s="28"/>
+      <c r="AF18" s="28"/>
+      <c r="AG18" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH18" s="3"/>
+      <c r="AI18" s="3"/>
+    </row>
+    <row r="19" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="3"/>
+      <c r="AD20" s="3"/>
+      <c r="AE20" s="3"/>
+      <c r="AF20" s="3"/>
+      <c r="AG20" s="3"/>
+      <c r="AH20" s="3"/>
+      <c r="AI20" s="3"/>
+    </row>
+    <row r="21" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="3"/>
+      <c r="AD21" s="3"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="3"/>
+      <c r="AH21" s="3"/>
+      <c r="AI21" s="3"/>
+    </row>
+    <row r="22" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH22" s="3"/>
+      <c r="AI22" s="3"/>
+    </row>
+    <row r="23" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC23" s="3"/>
+      <c r="AD23" s="3"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH23" s="3"/>
+      <c r="AI23" s="3"/>
+    </row>
+    <row r="24" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="3"/>
+      <c r="AH24" s="3"/>
+      <c r="AI24" s="3"/>
+    </row>
+    <row r="25" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="3"/>
+      <c r="AH25" s="3"/>
+      <c r="AI25" s="3"/>
+    </row>
+    <row r="26" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="3"/>
+      <c r="AC26" s="3"/>
+      <c r="AD26" s="3"/>
+      <c r="AE26" s="3"/>
+      <c r="AF26" s="3"/>
+      <c r="AG26" s="3"/>
+      <c r="AH26" s="3"/>
+      <c r="AI26" s="3"/>
+    </row>
+    <row r="27" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X27" s="3"/>
+      <c r="Y27" s="3"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
+      <c r="AB27" s="3"/>
+      <c r="AC27" s="3"/>
+      <c r="AD27" s="3"/>
+      <c r="AE27" s="3"/>
+      <c r="AF27" s="3"/>
+      <c r="AG27" s="3"/>
+      <c r="AH27" s="3"/>
+      <c r="AI27" s="3"/>
+    </row>
+    <row r="28" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X28" s="3"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC28" s="3"/>
+      <c r="AD28" s="3"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="3"/>
+    </row>
+    <row r="29" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X29" s="3"/>
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
+      <c r="AB29" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC29" s="3"/>
+      <c r="AD29" s="3"/>
+      <c r="AE29" s="3"/>
+      <c r="AF29" s="3"/>
+      <c r="AG29" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH29" s="3"/>
+      <c r="AI29" s="3"/>
+    </row>
+    <row r="30" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X30" s="3"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
+      <c r="AB30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC30" s="3"/>
+      <c r="AD30" s="3"/>
+      <c r="AE30" s="3"/>
+      <c r="AF30" s="3"/>
+      <c r="AG30" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH30" s="3"/>
+      <c r="AI30" s="3"/>
+    </row>
+    <row r="31" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X31" s="3"/>
+      <c r="Y31" s="3"/>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
+      <c r="AB31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC31" s="3"/>
+      <c r="AD31" s="3"/>
+      <c r="AE31" s="3"/>
+      <c r="AF31" s="3"/>
+      <c r="AG31" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH31" s="3"/>
+      <c r="AI31" s="3"/>
+    </row>
+    <row r="32" spans="24:35" x14ac:dyDescent="0.25">
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
+      <c r="AB32" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC32" s="3"/>
+      <c r="AD32" s="3"/>
+      <c r="AE32" s="3"/>
+      <c r="AF32" s="3"/>
+      <c r="AG32" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH32" s="3"/>
+      <c r="AI32" s="3"/>
+    </row>
+    <row r="33" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X33" s="3"/>
+      <c r="Y33" s="3"/>
+      <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
+      <c r="AB33" s="3"/>
+      <c r="AC33" s="3"/>
+      <c r="AD33" s="3"/>
+      <c r="AE33" s="3"/>
+      <c r="AF33" s="3"/>
+      <c r="AG33" s="3"/>
+      <c r="AH33" s="3"/>
+      <c r="AI33" s="3"/>
+    </row>
+    <row r="34" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="3"/>
+      <c r="AB34" s="3"/>
+      <c r="AC34" s="3"/>
+      <c r="AD34" s="3"/>
+      <c r="AE34" s="3"/>
+      <c r="AF34" s="3"/>
+      <c r="AG34" s="3"/>
+      <c r="AH34" s="3"/>
+      <c r="AI34" s="3"/>
+    </row>
+    <row r="35" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X35" s="3"/>
+      <c r="Y35" s="3"/>
+      <c r="Z35" s="3"/>
+      <c r="AA35" s="3"/>
+      <c r="AB35" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC35" s="3"/>
+      <c r="AD35" s="3"/>
+      <c r="AE35" s="3"/>
+      <c r="AF35" s="3"/>
+      <c r="AG35" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AH35" s="3"/>
+      <c r="AI35" s="3"/>
+    </row>
+    <row r="36" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X36" s="3"/>
+      <c r="Y36" s="3"/>
+      <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
+      <c r="AB36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC36" s="3"/>
+      <c r="AD36" s="3"/>
+      <c r="AE36" s="3"/>
+      <c r="AF36" s="3"/>
+      <c r="AG36" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AH36" s="3"/>
+      <c r="AI36" s="3"/>
+    </row>
+    <row r="37" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X37" s="3"/>
+      <c r="Y37" s="3"/>
+      <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
+      <c r="AB37" s="3"/>
+      <c r="AC37" s="3"/>
+      <c r="AD37" s="3"/>
+      <c r="AE37" s="3"/>
+      <c r="AF37" s="3"/>
+      <c r="AG37" s="3"/>
+      <c r="AH37" s="3"/>
+      <c r="AI37" s="3"/>
+    </row>
+    <row r="38" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
+      <c r="AB38" s="3"/>
+      <c r="AC38" s="3"/>
+      <c r="AD38" s="3"/>
+      <c r="AE38" s="3"/>
+      <c r="AF38" s="3"/>
+      <c r="AG38" s="3"/>
+      <c r="AH38" s="3"/>
+      <c r="AI38" s="3"/>
+    </row>
+    <row r="39" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E40" s="1"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X41" s="3"/>
+      <c r="Y41" s="3"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
+      <c r="AB41" s="3"/>
+      <c r="AC41" s="3"/>
+      <c r="AD41" s="3"/>
+      <c r="AE41" s="3"/>
+      <c r="AF41" s="3"/>
+      <c r="AG41" s="3"/>
+      <c r="AH41" s="3"/>
+      <c r="AI41" s="3"/>
+    </row>
+    <row r="42" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+      <c r="Z42" s="3"/>
+      <c r="AA42" s="3"/>
+      <c r="AB42" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC42" s="3"/>
+      <c r="AD42" s="3"/>
+      <c r="AE42" s="3"/>
+      <c r="AF42" s="3"/>
+      <c r="AG42" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH42" s="3"/>
+      <c r="AI42" s="3"/>
+    </row>
+    <row r="43" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X43" s="3"/>
+      <c r="Y43" s="3"/>
+      <c r="Z43" s="3"/>
+      <c r="AA43" s="3"/>
+      <c r="AB43" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC43" s="3"/>
+      <c r="AD43" s="3"/>
+      <c r="AE43" s="3"/>
+      <c r="AF43" s="3"/>
+      <c r="AG43" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH43" s="3"/>
+      <c r="AI43" s="3"/>
+    </row>
+    <row r="44" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E44" s="1"/>
+      <c r="X44" s="3"/>
+      <c r="Y44" s="3"/>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="3"/>
+      <c r="AB44" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC44" s="3"/>
+      <c r="AD44" s="3"/>
+      <c r="AE44" s="3"/>
+      <c r="AF44" s="3"/>
+      <c r="AG44" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH44" s="3"/>
+      <c r="AI44" s="3"/>
+    </row>
+    <row r="45" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X45" s="3"/>
+      <c r="Y45" s="3"/>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="3"/>
+      <c r="AB45" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC45" s="3"/>
+      <c r="AD45" s="3"/>
+      <c r="AE45" s="3"/>
+      <c r="AF45" s="3"/>
+      <c r="AG45" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH45" s="3"/>
+      <c r="AI45" s="3"/>
+    </row>
+    <row r="46" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X46" s="3"/>
+      <c r="Y46" s="3"/>
+      <c r="Z46" s="3"/>
+      <c r="AA46" s="3"/>
+      <c r="AB46" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC46" s="3"/>
+      <c r="AD46" s="3"/>
+      <c r="AE46" s="3"/>
+      <c r="AF46" s="3"/>
+      <c r="AG46" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH46" s="3"/>
+      <c r="AI46" s="3"/>
+    </row>
+    <row r="47" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X47" s="3"/>
+      <c r="Y47" s="3"/>
+      <c r="Z47" s="3"/>
+      <c r="AA47" s="3"/>
+      <c r="AB47" s="3"/>
+      <c r="AC47" s="3"/>
+      <c r="AD47" s="3"/>
+      <c r="AE47" s="3"/>
+      <c r="AF47" s="3"/>
+      <c r="AG47" s="3"/>
+      <c r="AH47" s="3"/>
+      <c r="AI47" s="3"/>
+    </row>
+    <row r="48" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X48" s="3"/>
+      <c r="Y48" s="3"/>
+      <c r="Z48" s="3"/>
+      <c r="AA48" s="3"/>
+      <c r="AB48" s="3"/>
+      <c r="AC48" s="3"/>
+      <c r="AD48" s="3"/>
+      <c r="AE48" s="3"/>
+      <c r="AF48" s="3"/>
+      <c r="AG48" s="3"/>
+      <c r="AH48" s="3"/>
+      <c r="AI48" s="3"/>
+    </row>
+    <row r="49" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E49" s="1"/>
+      <c r="X49" s="3"/>
+      <c r="Y49" s="3"/>
+      <c r="Z49" s="3"/>
+      <c r="AA49" s="3"/>
+      <c r="AB49" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC49" s="3"/>
+      <c r="AD49" s="3"/>
+      <c r="AE49" s="3"/>
+      <c r="AF49" s="3"/>
+      <c r="AG49" s="3"/>
+      <c r="AH49" s="3"/>
+      <c r="AI49" s="3"/>
+    </row>
+    <row r="50" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X50" s="3"/>
+      <c r="Y50" s="3"/>
+      <c r="Z50" s="3"/>
+      <c r="AA50" s="3"/>
+      <c r="AB50" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC50" s="3"/>
+      <c r="AD50" s="3"/>
+      <c r="AE50" s="3"/>
+      <c r="AF50" s="3"/>
+      <c r="AG50" s="3"/>
+      <c r="AH50" s="3"/>
+      <c r="AI50" s="3"/>
+    </row>
+    <row r="51" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X51" s="3"/>
+      <c r="Y51" s="3"/>
+      <c r="Z51" s="3"/>
+      <c r="AA51" s="3"/>
+      <c r="AB51" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC51" s="3"/>
+      <c r="AD51" s="3"/>
+      <c r="AE51" s="3"/>
+      <c r="AF51" s="3"/>
+      <c r="AG51" s="3"/>
+      <c r="AH51" s="3"/>
+      <c r="AI51" s="3"/>
+    </row>
+    <row r="52" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X52" s="3"/>
+      <c r="Y52" s="3"/>
+      <c r="Z52" s="3"/>
+      <c r="AA52" s="3"/>
+      <c r="AB52" s="3"/>
+      <c r="AC52" s="3"/>
+      <c r="AD52" s="3"/>
+      <c r="AE52" s="3"/>
+      <c r="AF52" s="3"/>
+      <c r="AG52" s="3"/>
+      <c r="AH52" s="3"/>
+      <c r="AI52" s="3"/>
+    </row>
+    <row r="53" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X53" s="3"/>
+      <c r="Y53" s="3"/>
+      <c r="Z53" s="3"/>
+      <c r="AA53" s="3"/>
+      <c r="AB53" s="3"/>
+      <c r="AC53" s="3"/>
+      <c r="AD53" s="3"/>
+      <c r="AE53" s="3"/>
+      <c r="AF53" s="3"/>
+      <c r="AG53" s="3"/>
+      <c r="AH53" s="3"/>
+      <c r="AI53" s="3"/>
+    </row>
+    <row r="54" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X54" s="3"/>
+      <c r="Y54" s="3"/>
+      <c r="Z54" s="3"/>
+      <c r="AA54" s="3"/>
+      <c r="AB54" s="3"/>
+      <c r="AC54" s="3"/>
+      <c r="AD54" s="3"/>
+      <c r="AE54" s="3"/>
+      <c r="AF54" s="3"/>
+      <c r="AG54" s="3"/>
+      <c r="AH54" s="3"/>
+      <c r="AI54" s="3"/>
+    </row>
+    <row r="55" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X57" s="3"/>
+      <c r="Y57" s="3"/>
+      <c r="Z57" s="3"/>
+      <c r="AA57" s="3"/>
+      <c r="AB57" s="3"/>
+      <c r="AC57" s="3"/>
+      <c r="AD57" s="3"/>
+      <c r="AE57" s="3"/>
+      <c r="AF57" s="3"/>
+      <c r="AG57" s="3"/>
+      <c r="AH57" s="3"/>
+      <c r="AI57" s="3"/>
+    </row>
+    <row r="58" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X58" s="3"/>
+      <c r="Y58" s="3"/>
+      <c r="Z58" s="3"/>
+      <c r="AA58" s="3"/>
+      <c r="AB58" s="3"/>
+      <c r="AC58" s="3"/>
+      <c r="AD58" s="3"/>
+      <c r="AE58" s="3"/>
+      <c r="AF58" s="3"/>
+      <c r="AG58" s="3"/>
+      <c r="AH58" s="3"/>
+    </row>
+    <row r="59" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X59" s="3"/>
+      <c r="Y59" s="3"/>
+      <c r="Z59" s="3"/>
+      <c r="AA59" s="3"/>
+      <c r="AB59" s="3"/>
+      <c r="AC59" s="3"/>
+      <c r="AD59" s="3"/>
+      <c r="AE59" s="3"/>
+      <c r="AF59" s="3"/>
+      <c r="AG59" s="3"/>
+      <c r="AH59" s="3"/>
+    </row>
+    <row r="60" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="3"/>
+      <c r="AA60" s="3"/>
+      <c r="AB60" s="3"/>
+      <c r="AC60" s="3"/>
+      <c r="AD60" s="3"/>
+      <c r="AE60" s="3"/>
+      <c r="AF60" s="3"/>
+      <c r="AG60" s="3"/>
+      <c r="AH60" s="3"/>
+    </row>
+    <row r="61" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
+      <c r="AB61" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC61" s="3"/>
+      <c r="AD61" s="3"/>
+      <c r="AE61" s="3"/>
+      <c r="AF61" s="3"/>
+      <c r="AG61" s="3"/>
+      <c r="AH61" s="3"/>
+    </row>
+    <row r="62" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3"/>
+      <c r="Z62" s="3"/>
+      <c r="AA62" s="3"/>
+      <c r="AB62" s="3"/>
+      <c r="AC62" s="3"/>
+      <c r="AD62" s="3"/>
+      <c r="AE62" s="3"/>
+      <c r="AF62" s="3"/>
+      <c r="AG62" s="3"/>
+      <c r="AH62" s="3"/>
+    </row>
+    <row r="63" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X63" s="3"/>
+      <c r="Y63" s="3"/>
+      <c r="Z63" s="3"/>
+      <c r="AA63" s="3"/>
+      <c r="AB63" s="3"/>
+      <c r="AC63" s="3"/>
+      <c r="AD63" s="3"/>
+      <c r="AE63" s="3"/>
+      <c r="AF63" s="3"/>
+      <c r="AG63" s="3"/>
+      <c r="AH63" s="3"/>
+    </row>
+    <row r="64" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3"/>
+      <c r="Z64" s="3"/>
+      <c r="AA64" s="3"/>
+      <c r="AB64" s="3"/>
+      <c r="AC64" s="3"/>
+      <c r="AD64" s="3"/>
+      <c r="AE64" s="3"/>
+      <c r="AF64" s="3"/>
+      <c r="AG64" s="3"/>
+      <c r="AH64" s="3"/>
+    </row>
+    <row r="65" spans="24:34" x14ac:dyDescent="0.25">
+      <c r="X65" s="3"/>
+      <c r="Y65" s="3"/>
+      <c r="Z65" s="3"/>
+      <c r="AA65" s="3"/>
+      <c r="AB65" s="3"/>
+      <c r="AC65" s="3"/>
+      <c r="AD65" s="3"/>
+      <c r="AE65" s="3"/>
+      <c r="AF65" s="3"/>
+      <c r="AG65" s="3"/>
+      <c r="AH65" s="3"/>
+    </row>
+    <row r="66" spans="24:34" x14ac:dyDescent="0.25">
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="3"/>
+      <c r="AA66" s="3"/>
+      <c r="AB66" s="3"/>
+      <c r="AC66" s="3"/>
+      <c r="AD66" s="3"/>
+      <c r="AE66" s="3"/>
+      <c r="AF66" s="3"/>
+      <c r="AG66" s="3"/>
+      <c r="AH66" s="3"/>
+    </row>
+    <row r="67" spans="24:34" x14ac:dyDescent="0.25">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="24:34" x14ac:dyDescent="0.25">
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="3"/>
+      <c r="AA68" s="3"/>
+      <c r="AB68" s="3"/>
+      <c r="AC68" s="3"/>
+      <c r="AD68" s="3"/>
+      <c r="AE68" s="3"/>
+      <c r="AF68" s="3"/>
+      <c r="AG68" s="3"/>
+      <c r="AH68" s="3"/>
+    </row>
+    <row r="69" spans="24:34" x14ac:dyDescent="0.25">
+      <c r="X69" s="3"/>
+      <c r="Y69" s="3"/>
+      <c r="Z69" s="3"/>
+      <c r="AA69" s="3"/>
+      <c r="AB69" s="3"/>
+      <c r="AC69" s="3"/>
+      <c r="AD69" s="3"/>
+      <c r="AE69" s="3"/>
+      <c r="AF69" s="3"/>
+      <c r="AG69" s="3"/>
+      <c r="AH69" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
     <mergeCell ref="AA6:AC6"/>
     <mergeCell ref="Y6:Z6"/>
   </mergeCells>
@@ -17707,7 +23893,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AEB2071-28A2-48BB-B77C-31D6CC6F6BEA}">
   <dimension ref="B2:AG112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -21015,7 +27201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4653912-3521-498A-83FD-1BEDB9DB78BF}">
   <dimension ref="B2:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -21085,7 +27271,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD0ABB0-740C-45D8-A980-F8FD0FB04F00}">
   <dimension ref="B2:AA107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/_concept_6G_integration/MCS_Fall_Detection.xlsx
+++ b/_concept_6G_integration/MCS_Fall_Detection.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hayat\Documents\6G\FallDetection_new\_concept_6G_integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862AC03C-A186-4933-89C3-6974FDE1CC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6342B6-B155-47D2-B439-00880B043E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="-2970" windowWidth="23232" windowHeight="13872" firstSheet="1" activeTab="2" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
+    <workbookView xWindow="20544" yWindow="-2970" windowWidth="23232" windowHeight="13872" firstSheet="1" activeTab="4" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
   </bookViews>
   <sheets>
     <sheet name="Architecture (2)" sheetId="7" state="hidden" r:id="rId1"/>
     <sheet name="Architecture" sheetId="3" r:id="rId2"/>
     <sheet name="SequenceDiagram" sheetId="4" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
-    <sheet name="SequenceDiagram (2)" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="info to share" sheetId="8" r:id="rId5"/>
+    <sheet name="SequenceDiagram (2)" sheetId="5" state="hidden" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="119">
   <si>
     <t xml:space="preserve">Additional Components </t>
   </si>
@@ -317,6 +318,102 @@
   <si>
     <t>fall_dashboard background task</t>
   </si>
+  <si>
+    <t>which images are custom or public, hence which needs to be pushed to public registry</t>
+  </si>
+  <si>
+    <t>Document</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k8s </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient </t>
+  </si>
+  <si>
+    <t>Caregiver</t>
+  </si>
+  <si>
+    <t>Mobile app integration</t>
+  </si>
+  <si>
+    <t>web app integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which code/file is shared and which is not </t>
+  </si>
+  <si>
+    <t>Fall detection algorithm</t>
+  </si>
+  <si>
+    <t>Fall detection system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">what is the data input and what is the model and what is the output </t>
+  </si>
+  <si>
+    <t>how it is trained</t>
+  </si>
+  <si>
+    <t>how to manage model version</t>
+  </si>
+  <si>
+    <t>user flow (patient)</t>
+  </si>
+  <si>
+    <t>user flow (caregiver)</t>
+  </si>
+  <si>
+    <t>user flow (admin/tech)</t>
+  </si>
+  <si>
+    <t>data contract (expected shape of data input and output)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prerequisite </t>
+  </si>
+  <si>
+    <t>what is missing pieces</t>
+  </si>
+  <si>
+    <t>what should happen</t>
+  </si>
+  <si>
+    <t>location of existing pieces and how to talk to each compnent</t>
+  </si>
+  <si>
+    <t>how to monitor its health and how/when to  retrain</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Admin user</t>
+  </si>
+  <si>
+    <t>link to user flow (patient)</t>
+  </si>
+  <si>
+    <t>link to user flow (caregiver)</t>
+  </si>
+  <si>
+    <t>link to user flow (admin/tech)</t>
+  </si>
+  <si>
+    <t>architrecture overview + sequence diagram</t>
+  </si>
+  <si>
+    <t>internal info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">command list </t>
+  </si>
+  <si>
+    <t>override list</t>
+  </si>
+  <si>
+    <t>Step by step guide</t>
+  </si>
 </sst>
 </file>
 
@@ -440,7 +537,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -484,11 +581,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -537,11 +643,14 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22009,15 +22118,15 @@
     </row>
     <row r="6" spans="18:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="X6" s="3"/>
-      <c r="Y6" s="26" t="s">
+      <c r="Y6" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="Z6" s="26"/>
-      <c r="AA6" s="26" t="s">
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="AB6" s="26"/>
-      <c r="AC6" s="26"/>
+      <c r="AB6" s="28"/>
+      <c r="AC6" s="28"/>
       <c r="AD6" s="25"/>
       <c r="AE6" s="25"/>
       <c r="AF6" s="25"/>
@@ -22884,15 +22993,15 @@
     </row>
     <row r="6" spans="18:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="X6" s="3"/>
-      <c r="Y6" s="26" t="s">
+      <c r="Y6" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="Z6" s="26"/>
-      <c r="AA6" s="26" t="s">
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="AB6" s="26"/>
-      <c r="AC6" s="26"/>
+      <c r="AB6" s="28"/>
+      <c r="AC6" s="28"/>
       <c r="AD6" s="20"/>
       <c r="AE6" s="20"/>
       <c r="AF6" s="20"/>
@@ -23062,14 +23171,14 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-      <c r="AB16" s="28" t="s">
+      <c r="AB16" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="AC16" s="28"/>
-      <c r="AD16" s="28"/>
-      <c r="AE16" s="28"/>
-      <c r="AF16" s="28"/>
-      <c r="AG16" s="28" t="s">
+      <c r="AC16" s="27"/>
+      <c r="AD16" s="27"/>
+      <c r="AE16" s="27"/>
+      <c r="AF16" s="27"/>
+      <c r="AG16" s="27" t="s">
         <v>49</v>
       </c>
       <c r="AH16" s="3"/>
@@ -23080,14 +23189,14 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
-      <c r="AB17" s="28" t="s">
+      <c r="AB17" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="AC17" s="28"/>
-      <c r="AD17" s="28"/>
-      <c r="AE17" s="28"/>
-      <c r="AF17" s="28"/>
-      <c r="AG17" s="28" t="s">
+      <c r="AC17" s="27"/>
+      <c r="AD17" s="27"/>
+      <c r="AE17" s="27"/>
+      <c r="AF17" s="27"/>
+      <c r="AG17" s="27" t="s">
         <v>48</v>
       </c>
       <c r="AH17" s="3"/>
@@ -23098,14 +23207,14 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
-      <c r="AB18" s="28" t="s">
+      <c r="AB18" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="AC18" s="28"/>
-      <c r="AD18" s="28"/>
-      <c r="AE18" s="28"/>
-      <c r="AF18" s="28"/>
-      <c r="AG18" s="28" t="s">
+      <c r="AC18" s="27"/>
+      <c r="AD18" s="27"/>
+      <c r="AE18" s="27"/>
+      <c r="AF18" s="27"/>
+      <c r="AG18" s="27" t="s">
         <v>48</v>
       </c>
       <c r="AH18" s="3"/>
@@ -23257,7 +23366,7 @@
       <c r="AD28" s="3"/>
       <c r="AE28" s="3"/>
       <c r="AF28" s="3"/>
-      <c r="AG28" s="27" t="s">
+      <c r="AG28" s="26" t="s">
         <v>84</v>
       </c>
       <c r="AH28" s="3"/>
@@ -23275,7 +23384,7 @@
       <c r="AD29" s="3"/>
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
-      <c r="AG29" s="27" t="s">
+      <c r="AG29" s="26" t="s">
         <v>84</v>
       </c>
       <c r="AH29" s="3"/>
@@ -23293,7 +23402,7 @@
       <c r="AD30" s="3"/>
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
-      <c r="AG30" s="27" t="s">
+      <c r="AG30" s="26" t="s">
         <v>84</v>
       </c>
       <c r="AH30" s="3"/>
@@ -23311,7 +23420,7 @@
       <c r="AD31" s="3"/>
       <c r="AE31" s="3"/>
       <c r="AF31" s="3"/>
-      <c r="AG31" s="27" t="s">
+      <c r="AG31" s="26" t="s">
         <v>84</v>
       </c>
       <c r="AH31" s="3"/>
@@ -23329,7 +23438,7 @@
       <c r="AD32" s="3"/>
       <c r="AE32" s="3"/>
       <c r="AF32" s="3"/>
-      <c r="AG32" s="27" t="s">
+      <c r="AG32" s="26" t="s">
         <v>84</v>
       </c>
       <c r="AH32" s="3"/>
@@ -27272,6 +27381,185 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4BFEE13-EE03-4A51-A59E-ED03788FB866}">
+  <dimension ref="A2:C52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="2" max="2" width="78.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B52" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD0ABB0-740C-45D8-A980-F8FD0FB04F00}">
   <dimension ref="B2:AA107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/_concept_6G_integration/MCS_Fall_Detection.xlsx
+++ b/_concept_6G_integration/MCS_Fall_Detection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hayat\Documents\6G\FallDetection_new\_concept_6G_integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6342B6-B155-47D2-B439-00880B043E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE78E0D6-C7BE-4D51-A057-03681A93EA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="-2970" windowWidth="23232" windowHeight="13872" firstSheet="1" activeTab="4" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{55F2A534-9267-4FFE-9D89-C2FA8C43E60F}"/>
   </bookViews>
   <sheets>
     <sheet name="Architecture (2)" sheetId="7" state="hidden" r:id="rId1"/>
@@ -645,10 +645,10 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -6245,81 +6245,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>43253</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>100853</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>471207</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Rectangle 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35B312A7-5BA2-43C9-B0FA-C548BC32D814}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2463724" y="100853"/>
-          <a:ext cx="1033071" cy="290567"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Mobile App</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1200">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>29963</xdr:colOff>
       <xdr:row>20</xdr:row>
@@ -6456,81 +6381,6 @@
           <a:endParaRPr lang="en-DE" sz="1200">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>240477</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>96371</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>63312</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>5938</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="Rectangle 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10545403-86D7-453F-8402-DB1A02A20D9D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1450712" y="3525371"/>
-          <a:ext cx="1033071" cy="290567"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Backend</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1200">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -6679,81 +6529,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>420221</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>177140</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>219808</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>117524</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="Rectangle 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA2E3CA5-1436-4C6B-94F2-48CF8C7A06C1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1636490" y="8954794"/>
-          <a:ext cx="1623991" cy="321384"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1200">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Web App / Browser</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-DE" sz="1200">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>413117</xdr:colOff>
       <xdr:row>49</xdr:row>
@@ -6862,15 +6637,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>255631</xdr:colOff>
+      <xdr:colOff>233650</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>108205</xdr:rowOff>
+      <xdr:rowOff>93551</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>234461</xdr:colOff>
+      <xdr:colOff>212480</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>184405</xdr:rowOff>
+      <xdr:rowOff>169751</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6885,7 +6660,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4512573" y="9838359"/>
+          <a:off x="4490592" y="9911628"/>
           <a:ext cx="1195100" cy="647700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -11299,6 +11074,231 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>597063</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>169977</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>446943</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>131885</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35B312A7-5BA2-43C9-B0FA-C548BC32D814}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2421467" y="169977"/>
+          <a:ext cx="2282418" cy="342908"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Mobile App</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>242382</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>96371</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>398319</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>155864</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="Rectangle 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10545403-86D7-453F-8402-DB1A02A20D9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1454655" y="3663916"/>
+          <a:ext cx="1368209" cy="249993"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Backend</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>480093</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>126522</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>249115</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>109904</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectangle 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA2E3CA5-1436-4C6B-94F2-48CF8C7A06C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1696362" y="9182599"/>
+          <a:ext cx="2201561" cy="173882"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Web App / Browser</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-DE" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -13445,8 +13445,8 @@
       <xdr:rowOff>167641</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>516528</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>554935</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>167641</xdr:rowOff>
     </xdr:to>
@@ -13463,8 +13463,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9222650" y="6454141"/>
-          <a:ext cx="1657078" cy="0"/>
+          <a:off x="9272346" y="6644641"/>
+          <a:ext cx="5379589" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -22118,15 +22118,15 @@
     </row>
     <row r="6" spans="18:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="X6" s="3"/>
-      <c r="Y6" s="28" t="s">
+      <c r="Y6" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="Z6" s="28"/>
-      <c r="AA6" s="28" t="s">
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="AB6" s="28"/>
-      <c r="AC6" s="28"/>
+      <c r="AB6" s="29"/>
+      <c r="AC6" s="29"/>
       <c r="AD6" s="25"/>
       <c r="AE6" s="25"/>
       <c r="AF6" s="25"/>
@@ -22993,15 +22993,15 @@
     </row>
     <row r="6" spans="18:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="X6" s="3"/>
-      <c r="Y6" s="28" t="s">
+      <c r="Y6" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="Z6" s="28"/>
-      <c r="AA6" s="28" t="s">
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="AB6" s="28"/>
-      <c r="AC6" s="28"/>
+      <c r="AB6" s="29"/>
+      <c r="AC6" s="29"/>
       <c r="AD6" s="20"/>
       <c r="AE6" s="20"/>
       <c r="AF6" s="20"/>
@@ -27390,10 +27390,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="28" t="s">
         <v>109</v>
       </c>
     </row>
